--- a/image source/แบบบันทึกพัฒนาการ_ปฐมวัย_3-4ปี_2568.xlsx
+++ b/image source/แบบบันทึกพัฒนาการ_ปฐมวัย_3-4ปี_2568.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Desktop\Project\kinder-track\image source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE4C91C-AF7E-4710-8112-E7E68EDB0E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59AD525A-27EF-48BC-925D-FD24033A0E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ภาคเรียนที่ 1" sheetId="1" r:id="rId1"/>
@@ -552,36 +552,6 @@
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -680,6 +650,36 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -957,2983 +957,2994 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10"/>
-      <c r="AI1" s="10"/>
-      <c r="AJ1" s="10"/>
-      <c r="AK1" s="10"/>
-      <c r="AL1" s="10"/>
-      <c r="AM1" s="10"/>
-      <c r="AN1" s="10"/>
-      <c r="AO1" s="10"/>
-      <c r="AP1" s="10"/>
-      <c r="AQ1" s="10"/>
-      <c r="AR1" s="10"/>
-      <c r="AS1" s="10"/>
-      <c r="AT1" s="10"/>
-      <c r="AU1" s="10"/>
-      <c r="AV1" s="10"/>
-      <c r="AW1" s="10"/>
-      <c r="AX1" s="10"/>
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
     </row>
     <row r="2" spans="1:50" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="9"/>
-      <c r="AN2" s="9"/>
-      <c r="AO2" s="9"/>
-      <c r="AP2" s="9"/>
-      <c r="AQ2" s="9"/>
-      <c r="AR2" s="9"/>
-      <c r="AS2" s="9"/>
-      <c r="AT2" s="9"/>
-      <c r="AU2" s="9"/>
-      <c r="AV2" s="9"/>
-      <c r="AW2" s="9"/>
-      <c r="AX2" s="9"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="38"/>
+      <c r="AM2" s="38"/>
+      <c r="AN2" s="38"/>
+      <c r="AO2" s="38"/>
+      <c r="AP2" s="38"/>
+      <c r="AQ2" s="38"/>
+      <c r="AR2" s="38"/>
+      <c r="AS2" s="38"/>
+      <c r="AT2" s="38"/>
+      <c r="AU2" s="38"/>
+      <c r="AV2" s="38"/>
+      <c r="AW2" s="38"/>
+      <c r="AX2" s="38"/>
     </row>
     <row r="3" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7" t="s">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="7"/>
-      <c r="AF3" s="7"/>
-      <c r="AG3" s="7"/>
-      <c r="AH3" s="6" t="s">
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="40"/>
+      <c r="AB3" s="40"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="40"/>
+      <c r="AE3" s="40"/>
+      <c r="AF3" s="40"/>
+      <c r="AG3" s="40"/>
+      <c r="AH3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="6"/>
-      <c r="AM3" s="6"/>
-      <c r="AN3" s="6"/>
-      <c r="AO3" s="6"/>
-      <c r="AP3" s="6"/>
-      <c r="AQ3" s="6"/>
-      <c r="AR3" s="6"/>
-      <c r="AS3" s="6"/>
-      <c r="AT3" s="5" t="s">
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="41"/>
+      <c r="AN3" s="41"/>
+      <c r="AO3" s="41"/>
+      <c r="AP3" s="41"/>
+      <c r="AQ3" s="41"/>
+      <c r="AR3" s="41"/>
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="AU3" s="5"/>
-      <c r="AV3" s="5"/>
-      <c r="AW3" s="5"/>
-      <c r="AX3" s="5"/>
+      <c r="AU3" s="42"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
     </row>
     <row r="4" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3" t="s">
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3" t="s">
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3" t="s">
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3" t="s">
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3" t="s">
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3" t="s">
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="2" t="s">
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2" t="s">
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="35"/>
+      <c r="AK4" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2" t="s">
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="35"/>
+      <c r="AO4" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
-      <c r="AR4" s="2" t="s">
+      <c r="AP4" s="35"/>
+      <c r="AQ4" s="35"/>
+      <c r="AR4" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="12" t="s">
+      <c r="AS4" s="35"/>
+      <c r="AT4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AU4" s="12" t="s">
+      <c r="AU4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AV4" s="12" t="s">
+      <c r="AV4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AW4" s="12" t="s">
+      <c r="AW4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AX4" s="12" t="s">
+      <c r="AX4" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="N5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="R5" s="15" t="s">
+      <c r="R5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="S5" s="15" t="s">
+      <c r="S5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="T5" s="15" t="s">
+      <c r="T5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="U5" s="15" t="s">
+      <c r="U5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="V5" s="15" t="s">
+      <c r="V5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="W5" s="15" t="s">
+      <c r="W5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="X5" s="15" t="s">
+      <c r="X5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Y5" s="15" t="s">
+      <c r="Y5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="Z5" s="15" t="s">
+      <c r="Z5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA5" s="15" t="s">
+      <c r="AA5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AB5" s="15" t="s">
+      <c r="AB5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AC5" s="15" t="s">
+      <c r="AC5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AD5" s="15" t="s">
+      <c r="AD5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AE5" s="15" t="s">
+      <c r="AE5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AF5" s="15" t="s">
+      <c r="AF5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AG5" s="15" t="s">
+      <c r="AG5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AH5" s="16" t="s">
+      <c r="AH5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AI5" s="16" t="s">
+      <c r="AI5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AJ5" s="16" t="s">
+      <c r="AJ5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AK5" s="16" t="s">
+      <c r="AK5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AL5" s="16" t="s">
+      <c r="AL5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AM5" s="16" t="s">
+      <c r="AM5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AN5" s="16" t="s">
+      <c r="AN5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AO5" s="16" t="s">
+      <c r="AO5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AP5" s="16" t="s">
+      <c r="AP5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AQ5" s="16" t="s">
+      <c r="AQ5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AR5" s="16" t="s">
+      <c r="AR5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AS5" s="16" t="s">
+      <c r="AS5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AT5" s="17"/>
-      <c r="AU5" s="17"/>
-      <c r="AV5" s="17"/>
-      <c r="AW5" s="17"/>
-      <c r="AX5" s="17"/>
+      <c r="AT5" s="7"/>
+      <c r="AU5" s="7"/>
+      <c r="AV5" s="7"/>
+      <c r="AW5" s="7"/>
+      <c r="AX5" s="7"/>
     </row>
     <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="8">
         <v>1</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="20" t="str">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10" t="str">
         <f t="shared" ref="D6:D25" si="0">IFERROR(AVERAGE(B6:C6),"")</f>
         <v/>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="10" t="str">
         <f t="shared" ref="E6:E25" si="1">IFERROR(AVERAGE(B6:C6),"")</f>
         <v/>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20" t="str">
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10" t="str">
         <f t="shared" ref="H6:H25" si="2">IFERROR(AVERAGE(F6:G6),"")</f>
         <v/>
       </c>
-      <c r="I6" s="20" t="str">
+      <c r="I6" s="10" t="str">
         <f t="shared" ref="I6:I25" si="3">IFERROR(AVERAGE(F6:G6),"")</f>
         <v/>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="21" t="str">
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="11" t="str">
         <f t="shared" ref="L6:L25" si="4">IFERROR(AVERAGE(J6:K6),"")</f>
         <v/>
       </c>
-      <c r="M6" s="21" t="str">
+      <c r="M6" s="11" t="str">
         <f t="shared" ref="M6:M25" si="5">IFERROR(AVERAGE(J6:K6),"")</f>
         <v/>
       </c>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="21" t="str">
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="11" t="str">
         <f t="shared" ref="P6:P25" si="6">IFERROR(AVERAGE(N6:O6),"")</f>
         <v/>
       </c>
-      <c r="Q6" s="21" t="str">
+      <c r="Q6" s="11" t="str">
         <f t="shared" ref="Q6:Q25" si="7">IFERROR(AVERAGE(N6:O6),"")</f>
         <v/>
       </c>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="21" t="str">
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="11" t="str">
         <f t="shared" ref="T6:T25" si="8">IFERROR(AVERAGE(R6:S6),"")</f>
         <v/>
       </c>
-      <c r="U6" s="21" t="str">
+      <c r="U6" s="11" t="str">
         <f t="shared" ref="U6:U25" si="9">IFERROR(AVERAGE(R6:S6),"")</f>
         <v/>
       </c>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="21" t="str">
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="11" t="str">
         <f t="shared" ref="X6:X25" si="10">IFERROR(AVERAGE(V6:W6),"")</f>
         <v/>
       </c>
-      <c r="Y6" s="21" t="str">
+      <c r="Y6" s="11" t="str">
         <f t="shared" ref="Y6:Y25" si="11">IFERROR(AVERAGE(V6:W6),"")</f>
         <v/>
       </c>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="21" t="str">
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="11" t="str">
         <f t="shared" ref="AB6:AB25" si="12">IFERROR(AVERAGE(Z6:AA6),"")</f>
         <v/>
       </c>
-      <c r="AC6" s="21" t="str">
+      <c r="AC6" s="11" t="str">
         <f t="shared" ref="AC6:AC25" si="13">IFERROR(AVERAGE(Z6:AA6),"")</f>
         <v/>
       </c>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="21" t="str">
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="11" t="str">
         <f t="shared" ref="AF6:AF25" si="14">IFERROR(AVERAGE(AD6:AE6),"")</f>
         <v/>
       </c>
-      <c r="AG6" s="21" t="str">
+      <c r="AG6" s="11" t="str">
         <f t="shared" ref="AG6:AG25" si="15">IFERROR(AVERAGE(AD6:AE6),"")</f>
         <v/>
       </c>
-      <c r="AH6" s="19"/>
-      <c r="AI6" s="19"/>
-      <c r="AJ6" s="22" t="str">
+      <c r="AH6" s="9"/>
+      <c r="AI6" s="9"/>
+      <c r="AJ6" s="12" t="str">
         <f t="shared" ref="AJ6:AJ25" si="16">IFERROR(AVERAGE(AH6:AI6),"")</f>
         <v/>
       </c>
-      <c r="AK6" s="19"/>
-      <c r="AL6" s="19"/>
-      <c r="AM6" s="22" t="str">
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="12" t="str">
         <f t="shared" ref="AM6:AM25" si="17">IFERROR(AVERAGE(AK6:AL6),"")</f>
         <v/>
       </c>
-      <c r="AN6" s="22" t="str">
+      <c r="AN6" s="12" t="str">
         <f t="shared" ref="AN6:AN25" si="18">IFERROR(AVERAGE(AK6:AL6),"")</f>
         <v/>
       </c>
-      <c r="AO6" s="19"/>
-      <c r="AP6" s="19"/>
-      <c r="AQ6" s="22" t="str">
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="12" t="str">
         <f t="shared" ref="AQ6:AQ25" si="19">IFERROR(AVERAGE(AO6:AP6),"")</f>
         <v/>
       </c>
-      <c r="AR6" s="19"/>
-      <c r="AS6" s="22">
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="12">
         <f t="shared" ref="AS6:AS25" si="20">IFERROR(AR6,"")</f>
         <v>0</v>
       </c>
-      <c r="AT6" s="23" t="str">
+      <c r="AT6" s="13" t="str">
         <f t="shared" ref="AT6:AT25" si="21">IFERROR(AVERAGE(E6,I6),"")</f>
         <v/>
       </c>
-      <c r="AU6" s="23" t="str">
+      <c r="AU6" s="13" t="str">
         <f t="shared" ref="AU6:AU25" si="22">IFERROR(AVERAGE(M6,Q6,U6,Y6,AC6,AG6),"")</f>
         <v/>
       </c>
-      <c r="AV6" s="23">
+      <c r="AV6" s="13">
         <f t="shared" ref="AV6:AV25" si="23">IFERROR(AVERAGE(AJ6,AN6,AQ6,AS6),"")</f>
         <v>0</v>
       </c>
-      <c r="AW6" s="24">
+      <c r="AW6" s="14">
         <f t="shared" ref="AW6:AW25" si="24">IFERROR(AVERAGE(AT6:AV6),"")</f>
         <v>0</v>
       </c>
-      <c r="AX6" s="25"/>
+      <c r="AX6" s="15"/>
     </row>
     <row r="7" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="20" t="str">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E7" s="20" t="str">
+      <c r="E7" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="20" t="str">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I7" s="20" t="str">
+      <c r="I7" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="21" t="str">
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M7" s="21" t="str">
+      <c r="M7" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="21" t="str">
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q7" s="21" t="str">
+      <c r="Q7" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="21" t="str">
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U7" s="21" t="str">
+      <c r="U7" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V7" s="27"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="21" t="str">
+      <c r="V7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y7" s="21" t="str">
+      <c r="Y7" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z7" s="27"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="21" t="str">
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC7" s="21" t="str">
+      <c r="AC7" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD7" s="27"/>
-      <c r="AE7" s="27"/>
-      <c r="AF7" s="21" t="str">
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="17"/>
+      <c r="AF7" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG7" s="21" t="str">
+      <c r="AG7" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH7" s="27"/>
-      <c r="AI7" s="27"/>
-      <c r="AJ7" s="22" t="str">
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="17"/>
+      <c r="AJ7" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK7" s="27"/>
-      <c r="AL7" s="27"/>
-      <c r="AM7" s="22" t="str">
+      <c r="AK7" s="17"/>
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN7" s="22" t="str">
+      <c r="AN7" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO7" s="27"/>
-      <c r="AP7" s="27"/>
-      <c r="AQ7" s="22" t="str">
+      <c r="AO7" s="17"/>
+      <c r="AP7" s="17"/>
+      <c r="AQ7" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR7" s="27"/>
-      <c r="AS7" s="22">
+      <c r="AR7" s="17"/>
+      <c r="AS7" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT7" s="23" t="str">
+      <c r="AT7" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU7" s="23" t="str">
+      <c r="AU7" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV7" s="23">
+      <c r="AV7" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW7" s="24">
+      <c r="AW7" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX7" s="28"/>
+      <c r="AX7" s="18"/>
     </row>
     <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="A8" s="8">
         <v>3</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="20" t="str">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E8" s="20" t="str">
+      <c r="E8" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20" t="str">
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I8" s="20" t="str">
+      <c r="I8" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="21" t="str">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M8" s="21" t="str">
+      <c r="M8" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="21" t="str">
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q8" s="21" t="str">
+      <c r="Q8" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="21" t="str">
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U8" s="21" t="str">
+      <c r="U8" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="21" t="str">
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y8" s="21" t="str">
+      <c r="Y8" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="21" t="str">
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC8" s="21" t="str">
+      <c r="AC8" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="21" t="str">
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG8" s="21" t="str">
+      <c r="AG8" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH8" s="19"/>
-      <c r="AI8" s="19"/>
-      <c r="AJ8" s="22" t="str">
+      <c r="AH8" s="9"/>
+      <c r="AI8" s="9"/>
+      <c r="AJ8" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK8" s="19"/>
-      <c r="AL8" s="19"/>
-      <c r="AM8" s="22" t="str">
+      <c r="AK8" s="9"/>
+      <c r="AL8" s="9"/>
+      <c r="AM8" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN8" s="22" t="str">
+      <c r="AN8" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO8" s="19"/>
-      <c r="AP8" s="19"/>
-      <c r="AQ8" s="22" t="str">
+      <c r="AO8" s="9"/>
+      <c r="AP8" s="9"/>
+      <c r="AQ8" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="22">
+      <c r="AR8" s="9"/>
+      <c r="AS8" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT8" s="23" t="str">
+      <c r="AT8" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU8" s="23" t="str">
+      <c r="AU8" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV8" s="23">
+      <c r="AV8" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW8" s="24">
+      <c r="AW8" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX8" s="25"/>
+      <c r="AX8" s="15"/>
     </row>
     <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26">
+      <c r="A9" s="16">
         <v>4</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="20" t="str">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E9" s="20" t="str">
+      <c r="E9" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="20" t="str">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I9" s="20" t="str">
+      <c r="I9" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="21" t="str">
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M9" s="21" t="str">
+      <c r="M9" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="21" t="str">
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q9" s="21" t="str">
+      <c r="Q9" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="21" t="str">
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U9" s="21" t="str">
+      <c r="U9" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="21" t="str">
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y9" s="21" t="str">
+      <c r="Y9" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="21" t="str">
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC9" s="21" t="str">
+      <c r="AC9" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD9" s="27"/>
-      <c r="AE9" s="27"/>
-      <c r="AF9" s="21" t="str">
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG9" s="21" t="str">
+      <c r="AG9" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH9" s="27"/>
-      <c r="AI9" s="27"/>
-      <c r="AJ9" s="22" t="str">
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK9" s="27"/>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="22" t="str">
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN9" s="22" t="str">
+      <c r="AN9" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="27"/>
-      <c r="AQ9" s="22" t="str">
+      <c r="AO9" s="17"/>
+      <c r="AP9" s="17"/>
+      <c r="AQ9" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR9" s="27"/>
-      <c r="AS9" s="22">
+      <c r="AR9" s="17"/>
+      <c r="AS9" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT9" s="23" t="str">
+      <c r="AT9" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU9" s="23" t="str">
+      <c r="AU9" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV9" s="23">
+      <c r="AV9" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW9" s="24">
+      <c r="AW9" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX9" s="28"/>
+      <c r="AX9" s="18"/>
     </row>
     <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="A10" s="8">
         <v>5</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20" t="str">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E10" s="20" t="str">
+      <c r="E10" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20" t="str">
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I10" s="20" t="str">
+      <c r="I10" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="21" t="str">
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M10" s="21" t="str">
+      <c r="M10" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="21" t="str">
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q10" s="21" t="str">
+      <c r="Q10" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="21" t="str">
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U10" s="21" t="str">
+      <c r="U10" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="21" t="str">
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y10" s="21" t="str">
+      <c r="Y10" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="21" t="str">
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC10" s="21" t="str">
+      <c r="AC10" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="21" t="str">
+      <c r="AD10" s="9"/>
+      <c r="AE10" s="9"/>
+      <c r="AF10" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG10" s="21" t="str">
+      <c r="AG10" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH10" s="19"/>
-      <c r="AI10" s="19"/>
-      <c r="AJ10" s="22" t="str">
+      <c r="AH10" s="9"/>
+      <c r="AI10" s="9"/>
+      <c r="AJ10" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK10" s="19"/>
-      <c r="AL10" s="19"/>
-      <c r="AM10" s="22" t="str">
+      <c r="AK10" s="9"/>
+      <c r="AL10" s="9"/>
+      <c r="AM10" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN10" s="22" t="str">
+      <c r="AN10" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO10" s="19"/>
-      <c r="AP10" s="19"/>
-      <c r="AQ10" s="22" t="str">
+      <c r="AO10" s="9"/>
+      <c r="AP10" s="9"/>
+      <c r="AQ10" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR10" s="19"/>
-      <c r="AS10" s="22">
+      <c r="AR10" s="9"/>
+      <c r="AS10" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT10" s="23" t="str">
+      <c r="AT10" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU10" s="23" t="str">
+      <c r="AU10" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV10" s="23">
+      <c r="AV10" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW10" s="24">
+      <c r="AW10" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX10" s="25"/>
+      <c r="AX10" s="15"/>
     </row>
     <row r="11" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26">
+      <c r="A11" s="16">
         <v>6</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="20" t="str">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E11" s="20" t="str">
+      <c r="E11" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="20" t="str">
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I11" s="20" t="str">
+      <c r="I11" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="21" t="str">
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M11" s="21" t="str">
+      <c r="M11" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="21" t="str">
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q11" s="21" t="str">
+      <c r="Q11" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="21" t="str">
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U11" s="21" t="str">
+      <c r="U11" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="21" t="str">
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y11" s="21" t="str">
+      <c r="Y11" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z11" s="27"/>
-      <c r="AA11" s="27"/>
-      <c r="AB11" s="21" t="str">
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC11" s="21" t="str">
+      <c r="AC11" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD11" s="27"/>
-      <c r="AE11" s="27"/>
-      <c r="AF11" s="21" t="str">
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG11" s="21" t="str">
+      <c r="AG11" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH11" s="27"/>
-      <c r="AI11" s="27"/>
-      <c r="AJ11" s="22" t="str">
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK11" s="27"/>
-      <c r="AL11" s="27"/>
-      <c r="AM11" s="22" t="str">
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN11" s="22" t="str">
+      <c r="AN11" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO11" s="27"/>
-      <c r="AP11" s="27"/>
-      <c r="AQ11" s="22" t="str">
+      <c r="AO11" s="17"/>
+      <c r="AP11" s="17"/>
+      <c r="AQ11" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR11" s="27"/>
-      <c r="AS11" s="22">
+      <c r="AR11" s="17"/>
+      <c r="AS11" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT11" s="23" t="str">
+      <c r="AT11" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU11" s="23" t="str">
+      <c r="AU11" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV11" s="23">
+      <c r="AV11" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW11" s="24">
+      <c r="AW11" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX11" s="28"/>
+      <c r="AX11" s="18"/>
     </row>
     <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
+      <c r="A12" s="8">
         <v>7</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20" t="str">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E12" s="20" t="str">
+      <c r="E12" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20" t="str">
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I12" s="20" t="str">
+      <c r="I12" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="21" t="str">
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M12" s="21" t="str">
+      <c r="M12" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="21" t="str">
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q12" s="21" t="str">
+      <c r="Q12" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="21" t="str">
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U12" s="21" t="str">
+      <c r="U12" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="21" t="str">
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y12" s="21" t="str">
+      <c r="Y12" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="21" t="str">
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC12" s="21" t="str">
+      <c r="AC12" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD12" s="19"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="21" t="str">
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG12" s="21" t="str">
+      <c r="AG12" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH12" s="19"/>
-      <c r="AI12" s="19"/>
-      <c r="AJ12" s="22" t="str">
+      <c r="AH12" s="9"/>
+      <c r="AI12" s="9"/>
+      <c r="AJ12" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
-      <c r="AM12" s="22" t="str">
+      <c r="AK12" s="9"/>
+      <c r="AL12" s="9"/>
+      <c r="AM12" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN12" s="22" t="str">
+      <c r="AN12" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO12" s="19"/>
-      <c r="AP12" s="19"/>
-      <c r="AQ12" s="22" t="str">
+      <c r="AO12" s="9"/>
+      <c r="AP12" s="9"/>
+      <c r="AQ12" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR12" s="19"/>
-      <c r="AS12" s="22">
+      <c r="AR12" s="9"/>
+      <c r="AS12" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT12" s="23" t="str">
+      <c r="AT12" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU12" s="23" t="str">
+      <c r="AU12" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV12" s="23">
+      <c r="AV12" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW12" s="24">
+      <c r="AW12" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX12" s="25"/>
+      <c r="AX12" s="15"/>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26">
+      <c r="A13" s="16">
         <v>8</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="20" t="str">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E13" s="20" t="str">
+      <c r="E13" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="20" t="str">
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I13" s="20" t="str">
+      <c r="I13" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="21" t="str">
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M13" s="21" t="str">
+      <c r="M13" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="21" t="str">
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q13" s="21" t="str">
+      <c r="Q13" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="21" t="str">
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U13" s="21" t="str">
+      <c r="U13" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="21" t="str">
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y13" s="21" t="str">
+      <c r="Y13" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="21" t="str">
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC13" s="21" t="str">
+      <c r="AC13" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD13" s="27"/>
-      <c r="AE13" s="27"/>
-      <c r="AF13" s="21" t="str">
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG13" s="21" t="str">
+      <c r="AG13" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH13" s="27"/>
-      <c r="AI13" s="27"/>
-      <c r="AJ13" s="22" t="str">
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK13" s="27"/>
-      <c r="AL13" s="27"/>
-      <c r="AM13" s="22" t="str">
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN13" s="22" t="str">
+      <c r="AN13" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO13" s="27"/>
-      <c r="AP13" s="27"/>
-      <c r="AQ13" s="22" t="str">
+      <c r="AO13" s="17"/>
+      <c r="AP13" s="17"/>
+      <c r="AQ13" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR13" s="27"/>
-      <c r="AS13" s="22">
+      <c r="AR13" s="17"/>
+      <c r="AS13" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT13" s="23" t="str">
+      <c r="AT13" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU13" s="23" t="str">
+      <c r="AU13" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV13" s="23">
+      <c r="AV13" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW13" s="24">
+      <c r="AW13" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX13" s="28"/>
+      <c r="AX13" s="18"/>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+      <c r="A14" s="8">
         <v>9</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20" t="str">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E14" s="20" t="str">
+      <c r="E14" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20" t="str">
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I14" s="20" t="str">
+      <c r="I14" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="21" t="str">
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M14" s="21" t="str">
+      <c r="M14" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="21" t="str">
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q14" s="21" t="str">
+      <c r="Q14" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="21" t="str">
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U14" s="21" t="str">
+      <c r="U14" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="21" t="str">
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y14" s="21" t="str">
+      <c r="Y14" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="21" t="str">
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC14" s="21" t="str">
+      <c r="AC14" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD14" s="19"/>
-      <c r="AE14" s="19"/>
-      <c r="AF14" s="21" t="str">
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="9"/>
+      <c r="AF14" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG14" s="21" t="str">
+      <c r="AG14" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH14" s="19"/>
-      <c r="AI14" s="19"/>
-      <c r="AJ14" s="22" t="str">
+      <c r="AH14" s="9"/>
+      <c r="AI14" s="9"/>
+      <c r="AJ14" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
-      <c r="AM14" s="22" t="str">
+      <c r="AK14" s="9"/>
+      <c r="AL14" s="9"/>
+      <c r="AM14" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN14" s="22" t="str">
+      <c r="AN14" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO14" s="19"/>
-      <c r="AP14" s="19"/>
-      <c r="AQ14" s="22" t="str">
+      <c r="AO14" s="9"/>
+      <c r="AP14" s="9"/>
+      <c r="AQ14" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR14" s="19"/>
-      <c r="AS14" s="22">
+      <c r="AR14" s="9"/>
+      <c r="AS14" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT14" s="23" t="str">
+      <c r="AT14" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU14" s="23" t="str">
+      <c r="AU14" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV14" s="23">
+      <c r="AV14" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW14" s="24">
+      <c r="AW14" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX14" s="25"/>
+      <c r="AX14" s="15"/>
     </row>
     <row r="15" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26">
+      <c r="A15" s="16">
         <v>10</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="20" t="str">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E15" s="20" t="str">
+      <c r="E15" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="20" t="str">
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I15" s="20" t="str">
+      <c r="I15" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="21" t="str">
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M15" s="21" t="str">
+      <c r="M15" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="21" t="str">
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q15" s="21" t="str">
+      <c r="Q15" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R15" s="27"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="21" t="str">
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U15" s="21" t="str">
+      <c r="U15" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V15" s="27"/>
-      <c r="W15" s="27"/>
-      <c r="X15" s="21" t="str">
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y15" s="21" t="str">
+      <c r="Y15" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z15" s="27"/>
-      <c r="AA15" s="27"/>
-      <c r="AB15" s="21" t="str">
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC15" s="21" t="str">
+      <c r="AC15" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD15" s="27"/>
-      <c r="AE15" s="27"/>
-      <c r="AF15" s="21" t="str">
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
+      <c r="AF15" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG15" s="21" t="str">
+      <c r="AG15" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH15" s="27"/>
-      <c r="AI15" s="27"/>
-      <c r="AJ15" s="22" t="str">
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK15" s="27"/>
-      <c r="AL15" s="27"/>
-      <c r="AM15" s="22" t="str">
+      <c r="AK15" s="17"/>
+      <c r="AL15" s="17"/>
+      <c r="AM15" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN15" s="22" t="str">
+      <c r="AN15" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO15" s="27"/>
-      <c r="AP15" s="27"/>
-      <c r="AQ15" s="22" t="str">
+      <c r="AO15" s="17"/>
+      <c r="AP15" s="17"/>
+      <c r="AQ15" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR15" s="27"/>
-      <c r="AS15" s="22">
+      <c r="AR15" s="17"/>
+      <c r="AS15" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT15" s="23" t="str">
+      <c r="AT15" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU15" s="23" t="str">
+      <c r="AU15" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV15" s="23">
+      <c r="AV15" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW15" s="24">
+      <c r="AW15" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX15" s="28"/>
+      <c r="AX15" s="18"/>
     </row>
     <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18">
+      <c r="A16" s="8">
         <v>11</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="20" t="str">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E16" s="20" t="str">
+      <c r="E16" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="20" t="str">
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I16" s="20" t="str">
+      <c r="I16" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="21" t="str">
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M16" s="21" t="str">
+      <c r="M16" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="21" t="str">
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q16" s="21" t="str">
+      <c r="Q16" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="21" t="str">
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U16" s="21" t="str">
+      <c r="U16" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="21" t="str">
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y16" s="21" t="str">
+      <c r="Y16" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="21" t="str">
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC16" s="21" t="str">
+      <c r="AC16" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD16" s="19"/>
-      <c r="AE16" s="19"/>
-      <c r="AF16" s="21" t="str">
+      <c r="AD16" s="9"/>
+      <c r="AE16" s="9"/>
+      <c r="AF16" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG16" s="21" t="str">
+      <c r="AG16" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH16" s="19"/>
-      <c r="AI16" s="19"/>
-      <c r="AJ16" s="22" t="str">
+      <c r="AH16" s="9"/>
+      <c r="AI16" s="9"/>
+      <c r="AJ16" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK16" s="19"/>
-      <c r="AL16" s="19"/>
-      <c r="AM16" s="22" t="str">
+      <c r="AK16" s="9"/>
+      <c r="AL16" s="9"/>
+      <c r="AM16" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN16" s="22" t="str">
+      <c r="AN16" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO16" s="19"/>
-      <c r="AP16" s="19"/>
-      <c r="AQ16" s="22" t="str">
+      <c r="AO16" s="9"/>
+      <c r="AP16" s="9"/>
+      <c r="AQ16" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR16" s="19"/>
-      <c r="AS16" s="22">
+      <c r="AR16" s="9"/>
+      <c r="AS16" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT16" s="23" t="str">
+      <c r="AT16" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU16" s="23" t="str">
+      <c r="AU16" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV16" s="23">
+      <c r="AV16" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW16" s="24">
+      <c r="AW16" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX16" s="25"/>
+      <c r="AX16" s="15"/>
     </row>
     <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26">
+      <c r="A17" s="16">
         <v>12</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="20" t="str">
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E17" s="20" t="str">
+      <c r="E17" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="20" t="str">
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I17" s="20" t="str">
+      <c r="I17" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="21" t="str">
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M17" s="21" t="str">
+      <c r="M17" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="21" t="str">
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q17" s="21" t="str">
+      <c r="Q17" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R17" s="27"/>
-      <c r="S17" s="27"/>
-      <c r="T17" s="21" t="str">
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U17" s="21" t="str">
+      <c r="U17" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-      <c r="X17" s="21" t="str">
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y17" s="21" t="str">
+      <c r="Y17" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z17" s="27"/>
-      <c r="AA17" s="27"/>
-      <c r="AB17" s="21" t="str">
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC17" s="21" t="str">
+      <c r="AC17" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD17" s="27"/>
-      <c r="AE17" s="27"/>
-      <c r="AF17" s="21" t="str">
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
+      <c r="AF17" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG17" s="21" t="str">
+      <c r="AG17" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH17" s="27"/>
-      <c r="AI17" s="27"/>
-      <c r="AJ17" s="22" t="str">
+      <c r="AH17" s="17"/>
+      <c r="AI17" s="17"/>
+      <c r="AJ17" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK17" s="27"/>
-      <c r="AL17" s="27"/>
-      <c r="AM17" s="22" t="str">
+      <c r="AK17" s="17"/>
+      <c r="AL17" s="17"/>
+      <c r="AM17" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN17" s="22" t="str">
+      <c r="AN17" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO17" s="27"/>
-      <c r="AP17" s="27"/>
-      <c r="AQ17" s="22" t="str">
+      <c r="AO17" s="17"/>
+      <c r="AP17" s="17"/>
+      <c r="AQ17" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR17" s="27"/>
-      <c r="AS17" s="22">
+      <c r="AR17" s="17"/>
+      <c r="AS17" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT17" s="23" t="str">
+      <c r="AT17" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU17" s="23" t="str">
+      <c r="AU17" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV17" s="23">
+      <c r="AV17" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW17" s="24">
+      <c r="AW17" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX17" s="28"/>
+      <c r="AX17" s="18"/>
     </row>
     <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18">
+      <c r="A18" s="8">
         <v>13</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="20" t="str">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E18" s="20" t="str">
+      <c r="E18" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="20" t="str">
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I18" s="20" t="str">
+      <c r="I18" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="21" t="str">
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M18" s="21" t="str">
+      <c r="M18" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="21" t="str">
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q18" s="21" t="str">
+      <c r="Q18" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="21" t="str">
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U18" s="21" t="str">
+      <c r="U18" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="21" t="str">
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y18" s="21" t="str">
+      <c r="Y18" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="21" t="str">
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC18" s="21" t="str">
+      <c r="AC18" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD18" s="19"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="21" t="str">
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="9"/>
+      <c r="AF18" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG18" s="21" t="str">
+      <c r="AG18" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH18" s="19"/>
-      <c r="AI18" s="19"/>
-      <c r="AJ18" s="22" t="str">
+      <c r="AH18" s="9"/>
+      <c r="AI18" s="9"/>
+      <c r="AJ18" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK18" s="19"/>
-      <c r="AL18" s="19"/>
-      <c r="AM18" s="22" t="str">
+      <c r="AK18" s="9"/>
+      <c r="AL18" s="9"/>
+      <c r="AM18" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN18" s="22" t="str">
+      <c r="AN18" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO18" s="19"/>
-      <c r="AP18" s="19"/>
-      <c r="AQ18" s="22" t="str">
+      <c r="AO18" s="9"/>
+      <c r="AP18" s="9"/>
+      <c r="AQ18" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR18" s="19"/>
-      <c r="AS18" s="22">
+      <c r="AR18" s="9"/>
+      <c r="AS18" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT18" s="23" t="str">
+      <c r="AT18" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU18" s="23" t="str">
+      <c r="AU18" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV18" s="23">
+      <c r="AV18" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW18" s="24">
+      <c r="AW18" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX18" s="25"/>
+      <c r="AX18" s="15"/>
     </row>
     <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26">
+      <c r="A19" s="16">
         <v>14</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="20" t="str">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E19" s="20" t="str">
+      <c r="E19" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="20" t="str">
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I19" s="20" t="str">
+      <c r="I19" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="21" t="str">
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M19" s="21" t="str">
+      <c r="M19" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="21" t="str">
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q19" s="21" t="str">
+      <c r="Q19" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="21" t="str">
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U19" s="21" t="str">
+      <c r="U19" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="21" t="str">
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y19" s="21" t="str">
+      <c r="Y19" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z19" s="27"/>
-      <c r="AA19" s="27"/>
-      <c r="AB19" s="21" t="str">
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC19" s="21" t="str">
+      <c r="AC19" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD19" s="27"/>
-      <c r="AE19" s="27"/>
-      <c r="AF19" s="21" t="str">
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG19" s="21" t="str">
+      <c r="AG19" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH19" s="27"/>
-      <c r="AI19" s="27"/>
-      <c r="AJ19" s="22" t="str">
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK19" s="27"/>
-      <c r="AL19" s="27"/>
-      <c r="AM19" s="22" t="str">
+      <c r="AK19" s="17"/>
+      <c r="AL19" s="17"/>
+      <c r="AM19" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN19" s="22" t="str">
+      <c r="AN19" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO19" s="27"/>
-      <c r="AP19" s="27"/>
-      <c r="AQ19" s="22" t="str">
+      <c r="AO19" s="17"/>
+      <c r="AP19" s="17"/>
+      <c r="AQ19" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR19" s="27"/>
-      <c r="AS19" s="22">
+      <c r="AR19" s="17"/>
+      <c r="AS19" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT19" s="23" t="str">
+      <c r="AT19" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU19" s="23" t="str">
+      <c r="AU19" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV19" s="23">
+      <c r="AV19" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW19" s="24">
+      <c r="AW19" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX19" s="28"/>
+      <c r="AX19" s="18"/>
     </row>
     <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18">
+      <c r="A20" s="8">
         <v>15</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="20" t="str">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E20" s="20" t="str">
+      <c r="E20" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20" t="str">
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I20" s="20" t="str">
+      <c r="I20" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="21" t="str">
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M20" s="21" t="str">
+      <c r="M20" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="21" t="str">
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q20" s="21" t="str">
+      <c r="Q20" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="21" t="str">
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U20" s="21" t="str">
+      <c r="U20" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="21" t="str">
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y20" s="21" t="str">
+      <c r="Y20" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="19"/>
-      <c r="AB20" s="21" t="str">
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC20" s="21" t="str">
+      <c r="AC20" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD20" s="19"/>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="21" t="str">
+      <c r="AD20" s="9"/>
+      <c r="AE20" s="9"/>
+      <c r="AF20" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG20" s="21" t="str">
+      <c r="AG20" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH20" s="19"/>
-      <c r="AI20" s="19"/>
-      <c r="AJ20" s="22" t="str">
+      <c r="AH20" s="9"/>
+      <c r="AI20" s="9"/>
+      <c r="AJ20" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="22" t="str">
+      <c r="AK20" s="9"/>
+      <c r="AL20" s="9"/>
+      <c r="AM20" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN20" s="22" t="str">
+      <c r="AN20" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO20" s="19"/>
-      <c r="AP20" s="19"/>
-      <c r="AQ20" s="22" t="str">
+      <c r="AO20" s="9"/>
+      <c r="AP20" s="9"/>
+      <c r="AQ20" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR20" s="19"/>
-      <c r="AS20" s="22">
+      <c r="AR20" s="9"/>
+      <c r="AS20" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT20" s="23" t="str">
+      <c r="AT20" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU20" s="23" t="str">
+      <c r="AU20" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV20" s="23">
+      <c r="AV20" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW20" s="24">
+      <c r="AW20" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX20" s="25"/>
+      <c r="AX20" s="15"/>
     </row>
     <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26">
+      <c r="A21" s="16">
         <v>16</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="20" t="str">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E21" s="20" t="str">
+      <c r="E21" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="20" t="str">
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I21" s="20" t="str">
+      <c r="I21" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="21" t="str">
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M21" s="21" t="str">
+      <c r="M21" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="21" t="str">
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q21" s="21" t="str">
+      <c r="Q21" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="21" t="str">
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U21" s="21" t="str">
+      <c r="U21" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V21" s="27"/>
-      <c r="W21" s="27"/>
-      <c r="X21" s="21" t="str">
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y21" s="21" t="str">
+      <c r="Y21" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z21" s="27"/>
-      <c r="AA21" s="27"/>
-      <c r="AB21" s="21" t="str">
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC21" s="21" t="str">
+      <c r="AC21" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD21" s="27"/>
-      <c r="AE21" s="27"/>
-      <c r="AF21" s="21" t="str">
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
+      <c r="AF21" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG21" s="21" t="str">
+      <c r="AG21" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH21" s="27"/>
-      <c r="AI21" s="27"/>
-      <c r="AJ21" s="22" t="str">
+      <c r="AH21" s="17"/>
+      <c r="AI21" s="17"/>
+      <c r="AJ21" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK21" s="27"/>
-      <c r="AL21" s="27"/>
-      <c r="AM21" s="22" t="str">
+      <c r="AK21" s="17"/>
+      <c r="AL21" s="17"/>
+      <c r="AM21" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN21" s="22" t="str">
+      <c r="AN21" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO21" s="27"/>
-      <c r="AP21" s="27"/>
-      <c r="AQ21" s="22" t="str">
+      <c r="AO21" s="17"/>
+      <c r="AP21" s="17"/>
+      <c r="AQ21" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR21" s="27"/>
-      <c r="AS21" s="22">
+      <c r="AR21" s="17"/>
+      <c r="AS21" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT21" s="23" t="str">
+      <c r="AT21" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU21" s="23" t="str">
+      <c r="AU21" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV21" s="23">
+      <c r="AV21" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW21" s="24">
+      <c r="AW21" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX21" s="28"/>
+      <c r="AX21" s="18"/>
     </row>
     <row r="22" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18">
+      <c r="A22" s="8">
         <v>17</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="20" t="str">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E22" s="20" t="str">
+      <c r="E22" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20" t="str">
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I22" s="20" t="str">
+      <c r="I22" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="21" t="str">
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M22" s="21" t="str">
+      <c r="M22" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="21" t="str">
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q22" s="21" t="str">
+      <c r="Q22" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="21" t="str">
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U22" s="21" t="str">
+      <c r="U22" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="21" t="str">
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y22" s="21" t="str">
+      <c r="Y22" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="21" t="str">
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC22" s="21" t="str">
+      <c r="AC22" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD22" s="19"/>
-      <c r="AE22" s="19"/>
-      <c r="AF22" s="21" t="str">
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG22" s="21" t="str">
+      <c r="AG22" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH22" s="19"/>
-      <c r="AI22" s="19"/>
-      <c r="AJ22" s="22" t="str">
+      <c r="AH22" s="9"/>
+      <c r="AI22" s="9"/>
+      <c r="AJ22" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK22" s="19"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="22" t="str">
+      <c r="AK22" s="9"/>
+      <c r="AL22" s="9"/>
+      <c r="AM22" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN22" s="22" t="str">
+      <c r="AN22" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO22" s="19"/>
-      <c r="AP22" s="19"/>
-      <c r="AQ22" s="22" t="str">
+      <c r="AO22" s="9"/>
+      <c r="AP22" s="9"/>
+      <c r="AQ22" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR22" s="19"/>
-      <c r="AS22" s="22">
+      <c r="AR22" s="9"/>
+      <c r="AS22" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT22" s="23" t="str">
+      <c r="AT22" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU22" s="23" t="str">
+      <c r="AU22" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV22" s="23">
+      <c r="AV22" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW22" s="24">
+      <c r="AW22" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX22" s="25"/>
+      <c r="AX22" s="15"/>
     </row>
     <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26">
+      <c r="A23" s="16">
         <v>18</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="20" t="str">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E23" s="20" t="str">
+      <c r="E23" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="20" t="str">
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I23" s="20" t="str">
+      <c r="I23" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="21" t="str">
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M23" s="21" t="str">
+      <c r="M23" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="21" t="str">
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q23" s="21" t="str">
+      <c r="Q23" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="21" t="str">
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U23" s="21" t="str">
+      <c r="U23" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="21" t="str">
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y23" s="21" t="str">
+      <c r="Y23" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="21" t="str">
+      <c r="Z23" s="17"/>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC23" s="21" t="str">
+      <c r="AC23" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD23" s="27"/>
-      <c r="AE23" s="27"/>
-      <c r="AF23" s="21" t="str">
+      <c r="AD23" s="17"/>
+      <c r="AE23" s="17"/>
+      <c r="AF23" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG23" s="21" t="str">
+      <c r="AG23" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH23" s="27"/>
-      <c r="AI23" s="27"/>
-      <c r="AJ23" s="22" t="str">
+      <c r="AH23" s="17"/>
+      <c r="AI23" s="17"/>
+      <c r="AJ23" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK23" s="27"/>
-      <c r="AL23" s="27"/>
-      <c r="AM23" s="22" t="str">
+      <c r="AK23" s="17"/>
+      <c r="AL23" s="17"/>
+      <c r="AM23" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN23" s="22" t="str">
+      <c r="AN23" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO23" s="27"/>
-      <c r="AP23" s="27"/>
-      <c r="AQ23" s="22" t="str">
+      <c r="AO23" s="17"/>
+      <c r="AP23" s="17"/>
+      <c r="AQ23" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR23" s="27"/>
-      <c r="AS23" s="22">
+      <c r="AR23" s="17"/>
+      <c r="AS23" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT23" s="23" t="str">
+      <c r="AT23" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU23" s="23" t="str">
+      <c r="AU23" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV23" s="23">
+      <c r="AV23" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW23" s="24">
+      <c r="AW23" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX23" s="28"/>
+      <c r="AX23" s="18"/>
     </row>
     <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18">
+      <c r="A24" s="8">
         <v>19</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="20" t="str">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E24" s="20" t="str">
+      <c r="E24" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20" t="str">
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I24" s="20" t="str">
+      <c r="I24" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="21" t="str">
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M24" s="21" t="str">
+      <c r="M24" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="21" t="str">
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q24" s="21" t="str">
+      <c r="Q24" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="21" t="str">
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U24" s="21" t="str">
+      <c r="U24" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="21" t="str">
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y24" s="21" t="str">
+      <c r="Y24" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="21" t="str">
+      <c r="Z24" s="9"/>
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC24" s="21" t="str">
+      <c r="AC24" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD24" s="19"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="21" t="str">
+      <c r="AD24" s="9"/>
+      <c r="AE24" s="9"/>
+      <c r="AF24" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG24" s="21" t="str">
+      <c r="AG24" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH24" s="19"/>
-      <c r="AI24" s="19"/>
-      <c r="AJ24" s="22" t="str">
+      <c r="AH24" s="9"/>
+      <c r="AI24" s="9"/>
+      <c r="AJ24" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK24" s="19"/>
-      <c r="AL24" s="19"/>
-      <c r="AM24" s="22" t="str">
+      <c r="AK24" s="9"/>
+      <c r="AL24" s="9"/>
+      <c r="AM24" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN24" s="22" t="str">
+      <c r="AN24" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO24" s="19"/>
-      <c r="AP24" s="19"/>
-      <c r="AQ24" s="22" t="str">
+      <c r="AO24" s="9"/>
+      <c r="AP24" s="9"/>
+      <c r="AQ24" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR24" s="19"/>
-      <c r="AS24" s="22">
+      <c r="AR24" s="9"/>
+      <c r="AS24" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT24" s="23" t="str">
+      <c r="AT24" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU24" s="23" t="str">
+      <c r="AU24" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV24" s="23">
+      <c r="AV24" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW24" s="24">
+      <c r="AW24" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX24" s="25"/>
+      <c r="AX24" s="15"/>
     </row>
     <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="26">
+      <c r="A25" s="16">
         <v>20</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="20" t="str">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E25" s="20" t="str">
+      <c r="E25" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="20" t="str">
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I25" s="20" t="str">
+      <c r="I25" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="21" t="str">
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M25" s="21" t="str">
+      <c r="M25" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="21" t="str">
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q25" s="21" t="str">
+      <c r="Q25" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="21" t="str">
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U25" s="21" t="str">
+      <c r="U25" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="21" t="str">
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y25" s="21" t="str">
+      <c r="Y25" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z25" s="27"/>
-      <c r="AA25" s="27"/>
-      <c r="AB25" s="21" t="str">
+      <c r="Z25" s="17"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC25" s="21" t="str">
+      <c r="AC25" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD25" s="27"/>
-      <c r="AE25" s="27"/>
-      <c r="AF25" s="21" t="str">
+      <c r="AD25" s="17"/>
+      <c r="AE25" s="17"/>
+      <c r="AF25" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG25" s="21" t="str">
+      <c r="AG25" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH25" s="27"/>
-      <c r="AI25" s="27"/>
-      <c r="AJ25" s="22" t="str">
+      <c r="AH25" s="17"/>
+      <c r="AI25" s="17"/>
+      <c r="AJ25" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK25" s="27"/>
-      <c r="AL25" s="27"/>
-      <c r="AM25" s="22" t="str">
+      <c r="AK25" s="17"/>
+      <c r="AL25" s="17"/>
+      <c r="AM25" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN25" s="22" t="str">
+      <c r="AN25" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO25" s="27"/>
-      <c r="AP25" s="27"/>
-      <c r="AQ25" s="22" t="str">
+      <c r="AO25" s="17"/>
+      <c r="AP25" s="17"/>
+      <c r="AQ25" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR25" s="27"/>
-      <c r="AS25" s="22">
+      <c r="AR25" s="17"/>
+      <c r="AS25" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT25" s="23" t="str">
+      <c r="AT25" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU25" s="23" t="str">
+      <c r="AU25" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV25" s="23">
+      <c r="AV25" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW25" s="24">
+      <c r="AW25" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX25" s="28"/>
+      <c r="AX25" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:AX1"/>
+    <mergeCell ref="A2:AX2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="J3:AG3"/>
+    <mergeCell ref="AH3:AS3"/>
+    <mergeCell ref="AT3:AX3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="R4:U4"/>
     <mergeCell ref="AO4:AQ4"/>
     <mergeCell ref="AR4:AS4"/>
     <mergeCell ref="V4:Y4"/>
@@ -3941,17 +3952,6 @@
     <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="AH4:AJ4"/>
     <mergeCell ref="AK4:AN4"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="A1:AX1"/>
-    <mergeCell ref="A2:AX2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="J3:AG3"/>
-    <mergeCell ref="AH3:AS3"/>
-    <mergeCell ref="AT3:AX3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="90" fitToWidth="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3969,2983 +3969,2994 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10"/>
-      <c r="AI1" s="10"/>
-      <c r="AJ1" s="10"/>
-      <c r="AK1" s="10"/>
-      <c r="AL1" s="10"/>
-      <c r="AM1" s="10"/>
-      <c r="AN1" s="10"/>
-      <c r="AO1" s="10"/>
-      <c r="AP1" s="10"/>
-      <c r="AQ1" s="10"/>
-      <c r="AR1" s="10"/>
-      <c r="AS1" s="10"/>
-      <c r="AT1" s="10"/>
-      <c r="AU1" s="10"/>
-      <c r="AV1" s="10"/>
-      <c r="AW1" s="10"/>
-      <c r="AX1" s="10"/>
+      <c r="A1" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
     </row>
     <row r="2" spans="1:50" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="9"/>
-      <c r="AN2" s="9"/>
-      <c r="AO2" s="9"/>
-      <c r="AP2" s="9"/>
-      <c r="AQ2" s="9"/>
-      <c r="AR2" s="9"/>
-      <c r="AS2" s="9"/>
-      <c r="AT2" s="9"/>
-      <c r="AU2" s="9"/>
-      <c r="AV2" s="9"/>
-      <c r="AW2" s="9"/>
-      <c r="AX2" s="9"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="38"/>
+      <c r="AM2" s="38"/>
+      <c r="AN2" s="38"/>
+      <c r="AO2" s="38"/>
+      <c r="AP2" s="38"/>
+      <c r="AQ2" s="38"/>
+      <c r="AR2" s="38"/>
+      <c r="AS2" s="38"/>
+      <c r="AT2" s="38"/>
+      <c r="AU2" s="38"/>
+      <c r="AV2" s="38"/>
+      <c r="AW2" s="38"/>
+      <c r="AX2" s="38"/>
     </row>
     <row r="3" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="7" t="s">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="7"/>
-      <c r="AF3" s="7"/>
-      <c r="AG3" s="7"/>
-      <c r="AH3" s="6" t="s">
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="40"/>
+      <c r="AB3" s="40"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="40"/>
+      <c r="AE3" s="40"/>
+      <c r="AF3" s="40"/>
+      <c r="AG3" s="40"/>
+      <c r="AH3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="6"/>
-      <c r="AM3" s="6"/>
-      <c r="AN3" s="6"/>
-      <c r="AO3" s="6"/>
-      <c r="AP3" s="6"/>
-      <c r="AQ3" s="6"/>
-      <c r="AR3" s="6"/>
-      <c r="AS3" s="6"/>
-      <c r="AT3" s="5" t="s">
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="41"/>
+      <c r="AN3" s="41"/>
+      <c r="AO3" s="41"/>
+      <c r="AP3" s="41"/>
+      <c r="AQ3" s="41"/>
+      <c r="AR3" s="41"/>
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="AU3" s="5"/>
-      <c r="AV3" s="5"/>
-      <c r="AW3" s="5"/>
-      <c r="AX3" s="5"/>
+      <c r="AU3" s="42"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
     </row>
     <row r="4" spans="1:50" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3" t="s">
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3" t="s">
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3" t="s">
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3" t="s">
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3" t="s">
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3" t="s">
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="2" t="s">
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2" t="s">
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="35"/>
+      <c r="AK4" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="AL4" s="2"/>
-      <c r="AM4" s="2"/>
-      <c r="AN4" s="2"/>
-      <c r="AO4" s="2" t="s">
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="35"/>
+      <c r="AO4" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="AP4" s="2"/>
-      <c r="AQ4" s="2"/>
-      <c r="AR4" s="2" t="s">
+      <c r="AP4" s="35"/>
+      <c r="AQ4" s="35"/>
+      <c r="AR4" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="12" t="s">
+      <c r="AS4" s="35"/>
+      <c r="AT4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AU4" s="12" t="s">
+      <c r="AU4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AV4" s="12" t="s">
+      <c r="AV4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AW4" s="12" t="s">
+      <c r="AW4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AX4" s="12" t="s">
+      <c r="AX4" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="15" t="s">
+      <c r="N5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="R5" s="15" t="s">
+      <c r="R5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="S5" s="15" t="s">
+      <c r="S5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="T5" s="15" t="s">
+      <c r="T5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="U5" s="15" t="s">
+      <c r="U5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="V5" s="15" t="s">
+      <c r="V5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="W5" s="15" t="s">
+      <c r="W5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="X5" s="15" t="s">
+      <c r="X5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Y5" s="15" t="s">
+      <c r="Y5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="Z5" s="15" t="s">
+      <c r="Z5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA5" s="15" t="s">
+      <c r="AA5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AB5" s="15" t="s">
+      <c r="AB5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AC5" s="15" t="s">
+      <c r="AC5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AD5" s="15" t="s">
+      <c r="AD5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AE5" s="15" t="s">
+      <c r="AE5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AF5" s="15" t="s">
+      <c r="AF5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AG5" s="15" t="s">
+      <c r="AG5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AH5" s="16" t="s">
+      <c r="AH5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AI5" s="16" t="s">
+      <c r="AI5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AJ5" s="16" t="s">
+      <c r="AJ5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AK5" s="16" t="s">
+      <c r="AK5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AL5" s="16" t="s">
+      <c r="AL5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AM5" s="16" t="s">
+      <c r="AM5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AN5" s="16" t="s">
+      <c r="AN5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AO5" s="16" t="s">
+      <c r="AO5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AP5" s="16" t="s">
+      <c r="AP5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AQ5" s="16" t="s">
+      <c r="AQ5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AR5" s="16" t="s">
+      <c r="AR5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AS5" s="16" t="s">
+      <c r="AS5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AT5" s="17"/>
-      <c r="AU5" s="17"/>
-      <c r="AV5" s="17"/>
-      <c r="AW5" s="17"/>
-      <c r="AX5" s="17"/>
+      <c r="AT5" s="7"/>
+      <c r="AU5" s="7"/>
+      <c r="AV5" s="7"/>
+      <c r="AW5" s="7"/>
+      <c r="AX5" s="7"/>
     </row>
     <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="8">
         <v>1</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="20" t="str">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10" t="str">
         <f t="shared" ref="D6:D25" si="0">IFERROR(AVERAGE(B6:C6),"")</f>
         <v/>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="10" t="str">
         <f t="shared" ref="E6:E25" si="1">IFERROR(AVERAGE(B6:C6),"")</f>
         <v/>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20" t="str">
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10" t="str">
         <f t="shared" ref="H6:H25" si="2">IFERROR(AVERAGE(F6:G6),"")</f>
         <v/>
       </c>
-      <c r="I6" s="20" t="str">
+      <c r="I6" s="10" t="str">
         <f t="shared" ref="I6:I25" si="3">IFERROR(AVERAGE(F6:G6),"")</f>
         <v/>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="21" t="str">
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="11" t="str">
         <f t="shared" ref="L6:L25" si="4">IFERROR(AVERAGE(J6:K6),"")</f>
         <v/>
       </c>
-      <c r="M6" s="21" t="str">
+      <c r="M6" s="11" t="str">
         <f t="shared" ref="M6:M25" si="5">IFERROR(AVERAGE(J6:K6),"")</f>
         <v/>
       </c>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="21" t="str">
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="11" t="str">
         <f t="shared" ref="P6:P25" si="6">IFERROR(AVERAGE(N6:O6),"")</f>
         <v/>
       </c>
-      <c r="Q6" s="21" t="str">
+      <c r="Q6" s="11" t="str">
         <f t="shared" ref="Q6:Q25" si="7">IFERROR(AVERAGE(N6:O6),"")</f>
         <v/>
       </c>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="21" t="str">
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="11" t="str">
         <f t="shared" ref="T6:T25" si="8">IFERROR(AVERAGE(R6:S6),"")</f>
         <v/>
       </c>
-      <c r="U6" s="21" t="str">
+      <c r="U6" s="11" t="str">
         <f t="shared" ref="U6:U25" si="9">IFERROR(AVERAGE(R6:S6),"")</f>
         <v/>
       </c>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="21" t="str">
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="11" t="str">
         <f t="shared" ref="X6:X25" si="10">IFERROR(AVERAGE(V6:W6),"")</f>
         <v/>
       </c>
-      <c r="Y6" s="21" t="str">
+      <c r="Y6" s="11" t="str">
         <f t="shared" ref="Y6:Y25" si="11">IFERROR(AVERAGE(V6:W6),"")</f>
         <v/>
       </c>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="21" t="str">
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="11" t="str">
         <f t="shared" ref="AB6:AB25" si="12">IFERROR(AVERAGE(Z6:AA6),"")</f>
         <v/>
       </c>
-      <c r="AC6" s="21" t="str">
+      <c r="AC6" s="11" t="str">
         <f t="shared" ref="AC6:AC25" si="13">IFERROR(AVERAGE(Z6:AA6),"")</f>
         <v/>
       </c>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="21" t="str">
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="11" t="str">
         <f t="shared" ref="AF6:AF25" si="14">IFERROR(AVERAGE(AD6:AE6),"")</f>
         <v/>
       </c>
-      <c r="AG6" s="21" t="str">
+      <c r="AG6" s="11" t="str">
         <f t="shared" ref="AG6:AG25" si="15">IFERROR(AVERAGE(AD6:AE6),"")</f>
         <v/>
       </c>
-      <c r="AH6" s="19"/>
-      <c r="AI6" s="19"/>
-      <c r="AJ6" s="22" t="str">
+      <c r="AH6" s="9"/>
+      <c r="AI6" s="9"/>
+      <c r="AJ6" s="12" t="str">
         <f t="shared" ref="AJ6:AJ25" si="16">IFERROR(AVERAGE(AH6:AI6),"")</f>
         <v/>
       </c>
-      <c r="AK6" s="19"/>
-      <c r="AL6" s="19"/>
-      <c r="AM6" s="22" t="str">
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="12" t="str">
         <f t="shared" ref="AM6:AM25" si="17">IFERROR(AVERAGE(AK6:AL6),"")</f>
         <v/>
       </c>
-      <c r="AN6" s="22" t="str">
+      <c r="AN6" s="12" t="str">
         <f t="shared" ref="AN6:AN25" si="18">IFERROR(AVERAGE(AK6:AL6),"")</f>
         <v/>
       </c>
-      <c r="AO6" s="19"/>
-      <c r="AP6" s="19"/>
-      <c r="AQ6" s="22" t="str">
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="12" t="str">
         <f t="shared" ref="AQ6:AQ25" si="19">IFERROR(AVERAGE(AO6:AP6),"")</f>
         <v/>
       </c>
-      <c r="AR6" s="19"/>
-      <c r="AS6" s="22">
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="12">
         <f t="shared" ref="AS6:AS25" si="20">IFERROR(AR6,"")</f>
         <v>0</v>
       </c>
-      <c r="AT6" s="23" t="str">
+      <c r="AT6" s="13" t="str">
         <f t="shared" ref="AT6:AT25" si="21">IFERROR(AVERAGE(E6,I6),"")</f>
         <v/>
       </c>
-      <c r="AU6" s="23" t="str">
+      <c r="AU6" s="13" t="str">
         <f t="shared" ref="AU6:AU25" si="22">IFERROR(AVERAGE(M6,Q6,U6,Y6,AC6,AG6),"")</f>
         <v/>
       </c>
-      <c r="AV6" s="23">
+      <c r="AV6" s="13">
         <f t="shared" ref="AV6:AV25" si="23">IFERROR(AVERAGE(AJ6,AN6,AQ6,AS6),"")</f>
         <v>0</v>
       </c>
-      <c r="AW6" s="24">
+      <c r="AW6" s="14">
         <f t="shared" ref="AW6:AW25" si="24">IFERROR(AVERAGE(AT6:AV6),"")</f>
         <v>0</v>
       </c>
-      <c r="AX6" s="25"/>
+      <c r="AX6" s="15"/>
     </row>
     <row r="7" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26">
+      <c r="A7" s="16">
         <v>2</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="20" t="str">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E7" s="20" t="str">
+      <c r="E7" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="20" t="str">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I7" s="20" t="str">
+      <c r="I7" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="21" t="str">
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M7" s="21" t="str">
+      <c r="M7" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="21" t="str">
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q7" s="21" t="str">
+      <c r="Q7" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="21" t="str">
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U7" s="21" t="str">
+      <c r="U7" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V7" s="27"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="21" t="str">
+      <c r="V7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y7" s="21" t="str">
+      <c r="Y7" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z7" s="27"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="21" t="str">
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC7" s="21" t="str">
+      <c r="AC7" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD7" s="27"/>
-      <c r="AE7" s="27"/>
-      <c r="AF7" s="21" t="str">
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="17"/>
+      <c r="AF7" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG7" s="21" t="str">
+      <c r="AG7" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH7" s="27"/>
-      <c r="AI7" s="27"/>
-      <c r="AJ7" s="22" t="str">
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="17"/>
+      <c r="AJ7" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK7" s="27"/>
-      <c r="AL7" s="27"/>
-      <c r="AM7" s="22" t="str">
+      <c r="AK7" s="17"/>
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN7" s="22" t="str">
+      <c r="AN7" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO7" s="27"/>
-      <c r="AP7" s="27"/>
-      <c r="AQ7" s="22" t="str">
+      <c r="AO7" s="17"/>
+      <c r="AP7" s="17"/>
+      <c r="AQ7" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR7" s="27"/>
-      <c r="AS7" s="22">
+      <c r="AR7" s="17"/>
+      <c r="AS7" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT7" s="23" t="str">
+      <c r="AT7" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU7" s="23" t="str">
+      <c r="AU7" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV7" s="23">
+      <c r="AV7" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW7" s="24">
+      <c r="AW7" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX7" s="28"/>
+      <c r="AX7" s="18"/>
     </row>
     <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="A8" s="8">
         <v>3</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="20" t="str">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E8" s="20" t="str">
+      <c r="E8" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20" t="str">
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I8" s="20" t="str">
+      <c r="I8" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="21" t="str">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M8" s="21" t="str">
+      <c r="M8" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="21" t="str">
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q8" s="21" t="str">
+      <c r="Q8" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="21" t="str">
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U8" s="21" t="str">
+      <c r="U8" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="21" t="str">
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y8" s="21" t="str">
+      <c r="Y8" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="21" t="str">
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC8" s="21" t="str">
+      <c r="AC8" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="21" t="str">
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG8" s="21" t="str">
+      <c r="AG8" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH8" s="19"/>
-      <c r="AI8" s="19"/>
-      <c r="AJ8" s="22" t="str">
+      <c r="AH8" s="9"/>
+      <c r="AI8" s="9"/>
+      <c r="AJ8" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK8" s="19"/>
-      <c r="AL8" s="19"/>
-      <c r="AM8" s="22" t="str">
+      <c r="AK8" s="9"/>
+      <c r="AL8" s="9"/>
+      <c r="AM8" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN8" s="22" t="str">
+      <c r="AN8" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO8" s="19"/>
-      <c r="AP8" s="19"/>
-      <c r="AQ8" s="22" t="str">
+      <c r="AO8" s="9"/>
+      <c r="AP8" s="9"/>
+      <c r="AQ8" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="22">
+      <c r="AR8" s="9"/>
+      <c r="AS8" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT8" s="23" t="str">
+      <c r="AT8" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU8" s="23" t="str">
+      <c r="AU8" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV8" s="23">
+      <c r="AV8" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW8" s="24">
+      <c r="AW8" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX8" s="25"/>
+      <c r="AX8" s="15"/>
     </row>
     <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26">
+      <c r="A9" s="16">
         <v>4</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="20" t="str">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E9" s="20" t="str">
+      <c r="E9" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="20" t="str">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I9" s="20" t="str">
+      <c r="I9" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="21" t="str">
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M9" s="21" t="str">
+      <c r="M9" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="21" t="str">
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q9" s="21" t="str">
+      <c r="Q9" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="21" t="str">
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U9" s="21" t="str">
+      <c r="U9" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="21" t="str">
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y9" s="21" t="str">
+      <c r="Y9" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="21" t="str">
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC9" s="21" t="str">
+      <c r="AC9" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD9" s="27"/>
-      <c r="AE9" s="27"/>
-      <c r="AF9" s="21" t="str">
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG9" s="21" t="str">
+      <c r="AG9" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH9" s="27"/>
-      <c r="AI9" s="27"/>
-      <c r="AJ9" s="22" t="str">
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK9" s="27"/>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="22" t="str">
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN9" s="22" t="str">
+      <c r="AN9" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="27"/>
-      <c r="AQ9" s="22" t="str">
+      <c r="AO9" s="17"/>
+      <c r="AP9" s="17"/>
+      <c r="AQ9" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR9" s="27"/>
-      <c r="AS9" s="22">
+      <c r="AR9" s="17"/>
+      <c r="AS9" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT9" s="23" t="str">
+      <c r="AT9" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU9" s="23" t="str">
+      <c r="AU9" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV9" s="23">
+      <c r="AV9" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW9" s="24">
+      <c r="AW9" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX9" s="28"/>
+      <c r="AX9" s="18"/>
     </row>
     <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="A10" s="8">
         <v>5</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20" t="str">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E10" s="20" t="str">
+      <c r="E10" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20" t="str">
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I10" s="20" t="str">
+      <c r="I10" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="21" t="str">
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M10" s="21" t="str">
+      <c r="M10" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="21" t="str">
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q10" s="21" t="str">
+      <c r="Q10" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="21" t="str">
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U10" s="21" t="str">
+      <c r="U10" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="21" t="str">
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y10" s="21" t="str">
+      <c r="Y10" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="21" t="str">
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC10" s="21" t="str">
+      <c r="AC10" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD10" s="19"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="21" t="str">
+      <c r="AD10" s="9"/>
+      <c r="AE10" s="9"/>
+      <c r="AF10" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG10" s="21" t="str">
+      <c r="AG10" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH10" s="19"/>
-      <c r="AI10" s="19"/>
-      <c r="AJ10" s="22" t="str">
+      <c r="AH10" s="9"/>
+      <c r="AI10" s="9"/>
+      <c r="AJ10" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK10" s="19"/>
-      <c r="AL10" s="19"/>
-      <c r="AM10" s="22" t="str">
+      <c r="AK10" s="9"/>
+      <c r="AL10" s="9"/>
+      <c r="AM10" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN10" s="22" t="str">
+      <c r="AN10" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO10" s="19"/>
-      <c r="AP10" s="19"/>
-      <c r="AQ10" s="22" t="str">
+      <c r="AO10" s="9"/>
+      <c r="AP10" s="9"/>
+      <c r="AQ10" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR10" s="19"/>
-      <c r="AS10" s="22">
+      <c r="AR10" s="9"/>
+      <c r="AS10" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT10" s="23" t="str">
+      <c r="AT10" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU10" s="23" t="str">
+      <c r="AU10" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV10" s="23">
+      <c r="AV10" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW10" s="24">
+      <c r="AW10" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX10" s="25"/>
+      <c r="AX10" s="15"/>
     </row>
     <row r="11" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26">
+      <c r="A11" s="16">
         <v>6</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="20" t="str">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E11" s="20" t="str">
+      <c r="E11" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="20" t="str">
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I11" s="20" t="str">
+      <c r="I11" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="21" t="str">
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M11" s="21" t="str">
+      <c r="M11" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="21" t="str">
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q11" s="21" t="str">
+      <c r="Q11" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="21" t="str">
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U11" s="21" t="str">
+      <c r="U11" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="21" t="str">
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y11" s="21" t="str">
+      <c r="Y11" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z11" s="27"/>
-      <c r="AA11" s="27"/>
-      <c r="AB11" s="21" t="str">
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC11" s="21" t="str">
+      <c r="AC11" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD11" s="27"/>
-      <c r="AE11" s="27"/>
-      <c r="AF11" s="21" t="str">
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG11" s="21" t="str">
+      <c r="AG11" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH11" s="27"/>
-      <c r="AI11" s="27"/>
-      <c r="AJ11" s="22" t="str">
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK11" s="27"/>
-      <c r="AL11" s="27"/>
-      <c r="AM11" s="22" t="str">
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN11" s="22" t="str">
+      <c r="AN11" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO11" s="27"/>
-      <c r="AP11" s="27"/>
-      <c r="AQ11" s="22" t="str">
+      <c r="AO11" s="17"/>
+      <c r="AP11" s="17"/>
+      <c r="AQ11" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR11" s="27"/>
-      <c r="AS11" s="22">
+      <c r="AR11" s="17"/>
+      <c r="AS11" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT11" s="23" t="str">
+      <c r="AT11" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU11" s="23" t="str">
+      <c r="AU11" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV11" s="23">
+      <c r="AV11" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW11" s="24">
+      <c r="AW11" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX11" s="28"/>
+      <c r="AX11" s="18"/>
     </row>
     <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
+      <c r="A12" s="8">
         <v>7</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20" t="str">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E12" s="20" t="str">
+      <c r="E12" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20" t="str">
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I12" s="20" t="str">
+      <c r="I12" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="21" t="str">
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M12" s="21" t="str">
+      <c r="M12" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="21" t="str">
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q12" s="21" t="str">
+      <c r="Q12" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="21" t="str">
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U12" s="21" t="str">
+      <c r="U12" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="21" t="str">
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y12" s="21" t="str">
+      <c r="Y12" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="21" t="str">
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC12" s="21" t="str">
+      <c r="AC12" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD12" s="19"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="21" t="str">
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG12" s="21" t="str">
+      <c r="AG12" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH12" s="19"/>
-      <c r="AI12" s="19"/>
-      <c r="AJ12" s="22" t="str">
+      <c r="AH12" s="9"/>
+      <c r="AI12" s="9"/>
+      <c r="AJ12" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
-      <c r="AM12" s="22" t="str">
+      <c r="AK12" s="9"/>
+      <c r="AL12" s="9"/>
+      <c r="AM12" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN12" s="22" t="str">
+      <c r="AN12" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO12" s="19"/>
-      <c r="AP12" s="19"/>
-      <c r="AQ12" s="22" t="str">
+      <c r="AO12" s="9"/>
+      <c r="AP12" s="9"/>
+      <c r="AQ12" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR12" s="19"/>
-      <c r="AS12" s="22">
+      <c r="AR12" s="9"/>
+      <c r="AS12" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT12" s="23" t="str">
+      <c r="AT12" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU12" s="23" t="str">
+      <c r="AU12" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV12" s="23">
+      <c r="AV12" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW12" s="24">
+      <c r="AW12" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX12" s="25"/>
+      <c r="AX12" s="15"/>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26">
+      <c r="A13" s="16">
         <v>8</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="20" t="str">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E13" s="20" t="str">
+      <c r="E13" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="20" t="str">
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I13" s="20" t="str">
+      <c r="I13" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="21" t="str">
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M13" s="21" t="str">
+      <c r="M13" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="21" t="str">
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q13" s="21" t="str">
+      <c r="Q13" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="21" t="str">
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U13" s="21" t="str">
+      <c r="U13" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="21" t="str">
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y13" s="21" t="str">
+      <c r="Y13" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="21" t="str">
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC13" s="21" t="str">
+      <c r="AC13" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD13" s="27"/>
-      <c r="AE13" s="27"/>
-      <c r="AF13" s="21" t="str">
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG13" s="21" t="str">
+      <c r="AG13" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH13" s="27"/>
-      <c r="AI13" s="27"/>
-      <c r="AJ13" s="22" t="str">
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK13" s="27"/>
-      <c r="AL13" s="27"/>
-      <c r="AM13" s="22" t="str">
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN13" s="22" t="str">
+      <c r="AN13" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO13" s="27"/>
-      <c r="AP13" s="27"/>
-      <c r="AQ13" s="22" t="str">
+      <c r="AO13" s="17"/>
+      <c r="AP13" s="17"/>
+      <c r="AQ13" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR13" s="27"/>
-      <c r="AS13" s="22">
+      <c r="AR13" s="17"/>
+      <c r="AS13" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT13" s="23" t="str">
+      <c r="AT13" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU13" s="23" t="str">
+      <c r="AU13" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV13" s="23">
+      <c r="AV13" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW13" s="24">
+      <c r="AW13" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX13" s="28"/>
+      <c r="AX13" s="18"/>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+      <c r="A14" s="8">
         <v>9</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20" t="str">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E14" s="20" t="str">
+      <c r="E14" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20" t="str">
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I14" s="20" t="str">
+      <c r="I14" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="21" t="str">
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M14" s="21" t="str">
+      <c r="M14" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="21" t="str">
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q14" s="21" t="str">
+      <c r="Q14" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="21" t="str">
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U14" s="21" t="str">
+      <c r="U14" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="21" t="str">
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y14" s="21" t="str">
+      <c r="Y14" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="21" t="str">
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC14" s="21" t="str">
+      <c r="AC14" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD14" s="19"/>
-      <c r="AE14" s="19"/>
-      <c r="AF14" s="21" t="str">
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="9"/>
+      <c r="AF14" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG14" s="21" t="str">
+      <c r="AG14" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH14" s="19"/>
-      <c r="AI14" s="19"/>
-      <c r="AJ14" s="22" t="str">
+      <c r="AH14" s="9"/>
+      <c r="AI14" s="9"/>
+      <c r="AJ14" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
-      <c r="AM14" s="22" t="str">
+      <c r="AK14" s="9"/>
+      <c r="AL14" s="9"/>
+      <c r="AM14" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN14" s="22" t="str">
+      <c r="AN14" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO14" s="19"/>
-      <c r="AP14" s="19"/>
-      <c r="AQ14" s="22" t="str">
+      <c r="AO14" s="9"/>
+      <c r="AP14" s="9"/>
+      <c r="AQ14" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR14" s="19"/>
-      <c r="AS14" s="22">
+      <c r="AR14" s="9"/>
+      <c r="AS14" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT14" s="23" t="str">
+      <c r="AT14" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU14" s="23" t="str">
+      <c r="AU14" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV14" s="23">
+      <c r="AV14" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW14" s="24">
+      <c r="AW14" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX14" s="25"/>
+      <c r="AX14" s="15"/>
     </row>
     <row r="15" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26">
+      <c r="A15" s="16">
         <v>10</v>
       </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="20" t="str">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E15" s="20" t="str">
+      <c r="E15" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="20" t="str">
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I15" s="20" t="str">
+      <c r="I15" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="21" t="str">
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M15" s="21" t="str">
+      <c r="M15" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="21" t="str">
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q15" s="21" t="str">
+      <c r="Q15" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R15" s="27"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="21" t="str">
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U15" s="21" t="str">
+      <c r="U15" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V15" s="27"/>
-      <c r="W15" s="27"/>
-      <c r="X15" s="21" t="str">
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y15" s="21" t="str">
+      <c r="Y15" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z15" s="27"/>
-      <c r="AA15" s="27"/>
-      <c r="AB15" s="21" t="str">
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC15" s="21" t="str">
+      <c r="AC15" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD15" s="27"/>
-      <c r="AE15" s="27"/>
-      <c r="AF15" s="21" t="str">
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
+      <c r="AF15" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG15" s="21" t="str">
+      <c r="AG15" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH15" s="27"/>
-      <c r="AI15" s="27"/>
-      <c r="AJ15" s="22" t="str">
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK15" s="27"/>
-      <c r="AL15" s="27"/>
-      <c r="AM15" s="22" t="str">
+      <c r="AK15" s="17"/>
+      <c r="AL15" s="17"/>
+      <c r="AM15" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN15" s="22" t="str">
+      <c r="AN15" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO15" s="27"/>
-      <c r="AP15" s="27"/>
-      <c r="AQ15" s="22" t="str">
+      <c r="AO15" s="17"/>
+      <c r="AP15" s="17"/>
+      <c r="AQ15" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR15" s="27"/>
-      <c r="AS15" s="22">
+      <c r="AR15" s="17"/>
+      <c r="AS15" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT15" s="23" t="str">
+      <c r="AT15" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU15" s="23" t="str">
+      <c r="AU15" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV15" s="23">
+      <c r="AV15" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW15" s="24">
+      <c r="AW15" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX15" s="28"/>
+      <c r="AX15" s="18"/>
     </row>
     <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18">
+      <c r="A16" s="8">
         <v>11</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="20" t="str">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E16" s="20" t="str">
+      <c r="E16" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="20" t="str">
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I16" s="20" t="str">
+      <c r="I16" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="21" t="str">
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M16" s="21" t="str">
+      <c r="M16" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="21" t="str">
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q16" s="21" t="str">
+      <c r="Q16" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="21" t="str">
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U16" s="21" t="str">
+      <c r="U16" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="21" t="str">
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y16" s="21" t="str">
+      <c r="Y16" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="21" t="str">
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC16" s="21" t="str">
+      <c r="AC16" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD16" s="19"/>
-      <c r="AE16" s="19"/>
-      <c r="AF16" s="21" t="str">
+      <c r="AD16" s="9"/>
+      <c r="AE16" s="9"/>
+      <c r="AF16" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG16" s="21" t="str">
+      <c r="AG16" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH16" s="19"/>
-      <c r="AI16" s="19"/>
-      <c r="AJ16" s="22" t="str">
+      <c r="AH16" s="9"/>
+      <c r="AI16" s="9"/>
+      <c r="AJ16" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK16" s="19"/>
-      <c r="AL16" s="19"/>
-      <c r="AM16" s="22" t="str">
+      <c r="AK16" s="9"/>
+      <c r="AL16" s="9"/>
+      <c r="AM16" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN16" s="22" t="str">
+      <c r="AN16" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO16" s="19"/>
-      <c r="AP16" s="19"/>
-      <c r="AQ16" s="22" t="str">
+      <c r="AO16" s="9"/>
+      <c r="AP16" s="9"/>
+      <c r="AQ16" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR16" s="19"/>
-      <c r="AS16" s="22">
+      <c r="AR16" s="9"/>
+      <c r="AS16" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT16" s="23" t="str">
+      <c r="AT16" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU16" s="23" t="str">
+      <c r="AU16" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV16" s="23">
+      <c r="AV16" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW16" s="24">
+      <c r="AW16" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX16" s="25"/>
+      <c r="AX16" s="15"/>
     </row>
     <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26">
+      <c r="A17" s="16">
         <v>12</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="20" t="str">
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E17" s="20" t="str">
+      <c r="E17" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="20" t="str">
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I17" s="20" t="str">
+      <c r="I17" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="21" t="str">
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M17" s="21" t="str">
+      <c r="M17" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="21" t="str">
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q17" s="21" t="str">
+      <c r="Q17" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R17" s="27"/>
-      <c r="S17" s="27"/>
-      <c r="T17" s="21" t="str">
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U17" s="21" t="str">
+      <c r="U17" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-      <c r="X17" s="21" t="str">
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y17" s="21" t="str">
+      <c r="Y17" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z17" s="27"/>
-      <c r="AA17" s="27"/>
-      <c r="AB17" s="21" t="str">
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC17" s="21" t="str">
+      <c r="AC17" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD17" s="27"/>
-      <c r="AE17" s="27"/>
-      <c r="AF17" s="21" t="str">
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
+      <c r="AF17" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG17" s="21" t="str">
+      <c r="AG17" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH17" s="27"/>
-      <c r="AI17" s="27"/>
-      <c r="AJ17" s="22" t="str">
+      <c r="AH17" s="17"/>
+      <c r="AI17" s="17"/>
+      <c r="AJ17" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK17" s="27"/>
-      <c r="AL17" s="27"/>
-      <c r="AM17" s="22" t="str">
+      <c r="AK17" s="17"/>
+      <c r="AL17" s="17"/>
+      <c r="AM17" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN17" s="22" t="str">
+      <c r="AN17" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO17" s="27"/>
-      <c r="AP17" s="27"/>
-      <c r="AQ17" s="22" t="str">
+      <c r="AO17" s="17"/>
+      <c r="AP17" s="17"/>
+      <c r="AQ17" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR17" s="27"/>
-      <c r="AS17" s="22">
+      <c r="AR17" s="17"/>
+      <c r="AS17" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT17" s="23" t="str">
+      <c r="AT17" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU17" s="23" t="str">
+      <c r="AU17" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV17" s="23">
+      <c r="AV17" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW17" s="24">
+      <c r="AW17" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX17" s="28"/>
+      <c r="AX17" s="18"/>
     </row>
     <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18">
+      <c r="A18" s="8">
         <v>13</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="20" t="str">
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E18" s="20" t="str">
+      <c r="E18" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="20" t="str">
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I18" s="20" t="str">
+      <c r="I18" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="21" t="str">
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M18" s="21" t="str">
+      <c r="M18" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="21" t="str">
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q18" s="21" t="str">
+      <c r="Q18" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="21" t="str">
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U18" s="21" t="str">
+      <c r="U18" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="21" t="str">
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y18" s="21" t="str">
+      <c r="Y18" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="21" t="str">
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC18" s="21" t="str">
+      <c r="AC18" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD18" s="19"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="21" t="str">
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="9"/>
+      <c r="AF18" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG18" s="21" t="str">
+      <c r="AG18" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH18" s="19"/>
-      <c r="AI18" s="19"/>
-      <c r="AJ18" s="22" t="str">
+      <c r="AH18" s="9"/>
+      <c r="AI18" s="9"/>
+      <c r="AJ18" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK18" s="19"/>
-      <c r="AL18" s="19"/>
-      <c r="AM18" s="22" t="str">
+      <c r="AK18" s="9"/>
+      <c r="AL18" s="9"/>
+      <c r="AM18" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN18" s="22" t="str">
+      <c r="AN18" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO18" s="19"/>
-      <c r="AP18" s="19"/>
-      <c r="AQ18" s="22" t="str">
+      <c r="AO18" s="9"/>
+      <c r="AP18" s="9"/>
+      <c r="AQ18" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR18" s="19"/>
-      <c r="AS18" s="22">
+      <c r="AR18" s="9"/>
+      <c r="AS18" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT18" s="23" t="str">
+      <c r="AT18" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU18" s="23" t="str">
+      <c r="AU18" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV18" s="23">
+      <c r="AV18" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW18" s="24">
+      <c r="AW18" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX18" s="25"/>
+      <c r="AX18" s="15"/>
     </row>
     <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26">
+      <c r="A19" s="16">
         <v>14</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="20" t="str">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E19" s="20" t="str">
+      <c r="E19" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="20" t="str">
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I19" s="20" t="str">
+      <c r="I19" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="21" t="str">
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M19" s="21" t="str">
+      <c r="M19" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="21" t="str">
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q19" s="21" t="str">
+      <c r="Q19" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="21" t="str">
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U19" s="21" t="str">
+      <c r="U19" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="21" t="str">
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y19" s="21" t="str">
+      <c r="Y19" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z19" s="27"/>
-      <c r="AA19" s="27"/>
-      <c r="AB19" s="21" t="str">
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC19" s="21" t="str">
+      <c r="AC19" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD19" s="27"/>
-      <c r="AE19" s="27"/>
-      <c r="AF19" s="21" t="str">
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG19" s="21" t="str">
+      <c r="AG19" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH19" s="27"/>
-      <c r="AI19" s="27"/>
-      <c r="AJ19" s="22" t="str">
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK19" s="27"/>
-      <c r="AL19" s="27"/>
-      <c r="AM19" s="22" t="str">
+      <c r="AK19" s="17"/>
+      <c r="AL19" s="17"/>
+      <c r="AM19" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN19" s="22" t="str">
+      <c r="AN19" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO19" s="27"/>
-      <c r="AP19" s="27"/>
-      <c r="AQ19" s="22" t="str">
+      <c r="AO19" s="17"/>
+      <c r="AP19" s="17"/>
+      <c r="AQ19" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR19" s="27"/>
-      <c r="AS19" s="22">
+      <c r="AR19" s="17"/>
+      <c r="AS19" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT19" s="23" t="str">
+      <c r="AT19" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU19" s="23" t="str">
+      <c r="AU19" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV19" s="23">
+      <c r="AV19" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW19" s="24">
+      <c r="AW19" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX19" s="28"/>
+      <c r="AX19" s="18"/>
     </row>
     <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18">
+      <c r="A20" s="8">
         <v>15</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="20" t="str">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E20" s="20" t="str">
+      <c r="E20" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20" t="str">
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I20" s="20" t="str">
+      <c r="I20" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="21" t="str">
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M20" s="21" t="str">
+      <c r="M20" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="21" t="str">
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q20" s="21" t="str">
+      <c r="Q20" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="21" t="str">
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U20" s="21" t="str">
+      <c r="U20" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="21" t="str">
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y20" s="21" t="str">
+      <c r="Y20" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="19"/>
-      <c r="AB20" s="21" t="str">
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC20" s="21" t="str">
+      <c r="AC20" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD20" s="19"/>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="21" t="str">
+      <c r="AD20" s="9"/>
+      <c r="AE20" s="9"/>
+      <c r="AF20" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG20" s="21" t="str">
+      <c r="AG20" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH20" s="19"/>
-      <c r="AI20" s="19"/>
-      <c r="AJ20" s="22" t="str">
+      <c r="AH20" s="9"/>
+      <c r="AI20" s="9"/>
+      <c r="AJ20" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="22" t="str">
+      <c r="AK20" s="9"/>
+      <c r="AL20" s="9"/>
+      <c r="AM20" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN20" s="22" t="str">
+      <c r="AN20" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO20" s="19"/>
-      <c r="AP20" s="19"/>
-      <c r="AQ20" s="22" t="str">
+      <c r="AO20" s="9"/>
+      <c r="AP20" s="9"/>
+      <c r="AQ20" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR20" s="19"/>
-      <c r="AS20" s="22">
+      <c r="AR20" s="9"/>
+      <c r="AS20" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT20" s="23" t="str">
+      <c r="AT20" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU20" s="23" t="str">
+      <c r="AU20" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV20" s="23">
+      <c r="AV20" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW20" s="24">
+      <c r="AW20" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX20" s="25"/>
+      <c r="AX20" s="15"/>
     </row>
     <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26">
+      <c r="A21" s="16">
         <v>16</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="20" t="str">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E21" s="20" t="str">
+      <c r="E21" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="20" t="str">
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I21" s="20" t="str">
+      <c r="I21" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="21" t="str">
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M21" s="21" t="str">
+      <c r="M21" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="21" t="str">
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q21" s="21" t="str">
+      <c r="Q21" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="21" t="str">
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U21" s="21" t="str">
+      <c r="U21" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V21" s="27"/>
-      <c r="W21" s="27"/>
-      <c r="X21" s="21" t="str">
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y21" s="21" t="str">
+      <c r="Y21" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z21" s="27"/>
-      <c r="AA21" s="27"/>
-      <c r="AB21" s="21" t="str">
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC21" s="21" t="str">
+      <c r="AC21" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD21" s="27"/>
-      <c r="AE21" s="27"/>
-      <c r="AF21" s="21" t="str">
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
+      <c r="AF21" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG21" s="21" t="str">
+      <c r="AG21" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH21" s="27"/>
-      <c r="AI21" s="27"/>
-      <c r="AJ21" s="22" t="str">
+      <c r="AH21" s="17"/>
+      <c r="AI21" s="17"/>
+      <c r="AJ21" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK21" s="27"/>
-      <c r="AL21" s="27"/>
-      <c r="AM21" s="22" t="str">
+      <c r="AK21" s="17"/>
+      <c r="AL21" s="17"/>
+      <c r="AM21" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN21" s="22" t="str">
+      <c r="AN21" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO21" s="27"/>
-      <c r="AP21" s="27"/>
-      <c r="AQ21" s="22" t="str">
+      <c r="AO21" s="17"/>
+      <c r="AP21" s="17"/>
+      <c r="AQ21" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR21" s="27"/>
-      <c r="AS21" s="22">
+      <c r="AR21" s="17"/>
+      <c r="AS21" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT21" s="23" t="str">
+      <c r="AT21" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU21" s="23" t="str">
+      <c r="AU21" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV21" s="23">
+      <c r="AV21" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW21" s="24">
+      <c r="AW21" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX21" s="28"/>
+      <c r="AX21" s="18"/>
     </row>
     <row r="22" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18">
+      <c r="A22" s="8">
         <v>17</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="20" t="str">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E22" s="20" t="str">
+      <c r="E22" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20" t="str">
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I22" s="20" t="str">
+      <c r="I22" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="21" t="str">
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M22" s="21" t="str">
+      <c r="M22" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="21" t="str">
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q22" s="21" t="str">
+      <c r="Q22" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="21" t="str">
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U22" s="21" t="str">
+      <c r="U22" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="21" t="str">
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y22" s="21" t="str">
+      <c r="Y22" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="21" t="str">
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC22" s="21" t="str">
+      <c r="AC22" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD22" s="19"/>
-      <c r="AE22" s="19"/>
-      <c r="AF22" s="21" t="str">
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG22" s="21" t="str">
+      <c r="AG22" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH22" s="19"/>
-      <c r="AI22" s="19"/>
-      <c r="AJ22" s="22" t="str">
+      <c r="AH22" s="9"/>
+      <c r="AI22" s="9"/>
+      <c r="AJ22" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK22" s="19"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="22" t="str">
+      <c r="AK22" s="9"/>
+      <c r="AL22" s="9"/>
+      <c r="AM22" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN22" s="22" t="str">
+      <c r="AN22" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO22" s="19"/>
-      <c r="AP22" s="19"/>
-      <c r="AQ22" s="22" t="str">
+      <c r="AO22" s="9"/>
+      <c r="AP22" s="9"/>
+      <c r="AQ22" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR22" s="19"/>
-      <c r="AS22" s="22">
+      <c r="AR22" s="9"/>
+      <c r="AS22" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT22" s="23" t="str">
+      <c r="AT22" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU22" s="23" t="str">
+      <c r="AU22" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV22" s="23">
+      <c r="AV22" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW22" s="24">
+      <c r="AW22" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX22" s="25"/>
+      <c r="AX22" s="15"/>
     </row>
     <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26">
+      <c r="A23" s="16">
         <v>18</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="20" t="str">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E23" s="20" t="str">
+      <c r="E23" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="20" t="str">
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I23" s="20" t="str">
+      <c r="I23" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="21" t="str">
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M23" s="21" t="str">
+      <c r="M23" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="21" t="str">
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q23" s="21" t="str">
+      <c r="Q23" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="21" t="str">
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U23" s="21" t="str">
+      <c r="U23" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="21" t="str">
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y23" s="21" t="str">
+      <c r="Y23" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="21" t="str">
+      <c r="Z23" s="17"/>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC23" s="21" t="str">
+      <c r="AC23" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD23" s="27"/>
-      <c r="AE23" s="27"/>
-      <c r="AF23" s="21" t="str">
+      <c r="AD23" s="17"/>
+      <c r="AE23" s="17"/>
+      <c r="AF23" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG23" s="21" t="str">
+      <c r="AG23" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH23" s="27"/>
-      <c r="AI23" s="27"/>
-      <c r="AJ23" s="22" t="str">
+      <c r="AH23" s="17"/>
+      <c r="AI23" s="17"/>
+      <c r="AJ23" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK23" s="27"/>
-      <c r="AL23" s="27"/>
-      <c r="AM23" s="22" t="str">
+      <c r="AK23" s="17"/>
+      <c r="AL23" s="17"/>
+      <c r="AM23" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN23" s="22" t="str">
+      <c r="AN23" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO23" s="27"/>
-      <c r="AP23" s="27"/>
-      <c r="AQ23" s="22" t="str">
+      <c r="AO23" s="17"/>
+      <c r="AP23" s="17"/>
+      <c r="AQ23" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR23" s="27"/>
-      <c r="AS23" s="22">
+      <c r="AR23" s="17"/>
+      <c r="AS23" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT23" s="23" t="str">
+      <c r="AT23" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU23" s="23" t="str">
+      <c r="AU23" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV23" s="23">
+      <c r="AV23" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW23" s="24">
+      <c r="AW23" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX23" s="28"/>
+      <c r="AX23" s="18"/>
     </row>
     <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18">
+      <c r="A24" s="8">
         <v>19</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="20" t="str">
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E24" s="20" t="str">
+      <c r="E24" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20" t="str">
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I24" s="20" t="str">
+      <c r="I24" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="21" t="str">
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M24" s="21" t="str">
+      <c r="M24" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="21" t="str">
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q24" s="21" t="str">
+      <c r="Q24" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="21" t="str">
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U24" s="21" t="str">
+      <c r="U24" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="21" t="str">
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y24" s="21" t="str">
+      <c r="Y24" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="21" t="str">
+      <c r="Z24" s="9"/>
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC24" s="21" t="str">
+      <c r="AC24" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD24" s="19"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="21" t="str">
+      <c r="AD24" s="9"/>
+      <c r="AE24" s="9"/>
+      <c r="AF24" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG24" s="21" t="str">
+      <c r="AG24" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH24" s="19"/>
-      <c r="AI24" s="19"/>
-      <c r="AJ24" s="22" t="str">
+      <c r="AH24" s="9"/>
+      <c r="AI24" s="9"/>
+      <c r="AJ24" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK24" s="19"/>
-      <c r="AL24" s="19"/>
-      <c r="AM24" s="22" t="str">
+      <c r="AK24" s="9"/>
+      <c r="AL24" s="9"/>
+      <c r="AM24" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN24" s="22" t="str">
+      <c r="AN24" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO24" s="19"/>
-      <c r="AP24" s="19"/>
-      <c r="AQ24" s="22" t="str">
+      <c r="AO24" s="9"/>
+      <c r="AP24" s="9"/>
+      <c r="AQ24" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR24" s="19"/>
-      <c r="AS24" s="22">
+      <c r="AR24" s="9"/>
+      <c r="AS24" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT24" s="23" t="str">
+      <c r="AT24" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU24" s="23" t="str">
+      <c r="AU24" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV24" s="23">
+      <c r="AV24" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW24" s="24">
+      <c r="AW24" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX24" s="25"/>
+      <c r="AX24" s="15"/>
     </row>
     <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="26">
+      <c r="A25" s="16">
         <v>20</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="20" t="str">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E25" s="20" t="str">
+      <c r="E25" s="10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="20" t="str">
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I25" s="20" t="str">
+      <c r="I25" s="10" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="21" t="str">
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="11" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M25" s="21" t="str">
+      <c r="M25" s="11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="21" t="str">
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="11" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q25" s="21" t="str">
+      <c r="Q25" s="11" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="21" t="str">
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="11" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="U25" s="21" t="str">
+      <c r="U25" s="11" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="21" t="str">
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="11" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y25" s="21" t="str">
+      <c r="Y25" s="11" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Z25" s="27"/>
-      <c r="AA25" s="27"/>
-      <c r="AB25" s="21" t="str">
+      <c r="Z25" s="17"/>
+      <c r="AA25" s="17"/>
+      <c r="AB25" s="11" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="AC25" s="21" t="str">
+      <c r="AC25" s="11" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AD25" s="27"/>
-      <c r="AE25" s="27"/>
-      <c r="AF25" s="21" t="str">
+      <c r="AD25" s="17"/>
+      <c r="AE25" s="17"/>
+      <c r="AF25" s="11" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AG25" s="21" t="str">
+      <c r="AG25" s="11" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AH25" s="27"/>
-      <c r="AI25" s="27"/>
-      <c r="AJ25" s="22" t="str">
+      <c r="AH25" s="17"/>
+      <c r="AI25" s="17"/>
+      <c r="AJ25" s="12" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AK25" s="27"/>
-      <c r="AL25" s="27"/>
-      <c r="AM25" s="22" t="str">
+      <c r="AK25" s="17"/>
+      <c r="AL25" s="17"/>
+      <c r="AM25" s="12" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AN25" s="22" t="str">
+      <c r="AN25" s="12" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AO25" s="27"/>
-      <c r="AP25" s="27"/>
-      <c r="AQ25" s="22" t="str">
+      <c r="AO25" s="17"/>
+      <c r="AP25" s="17"/>
+      <c r="AQ25" s="12" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="AR25" s="27"/>
-      <c r="AS25" s="22">
+      <c r="AR25" s="17"/>
+      <c r="AS25" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="AT25" s="23" t="str">
+      <c r="AT25" s="13" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="AU25" s="23" t="str">
+      <c r="AU25" s="13" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="AV25" s="23">
+      <c r="AV25" s="13">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="AW25" s="24">
+      <c r="AW25" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AX25" s="28"/>
+      <c r="AX25" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:AX1"/>
+    <mergeCell ref="A2:AX2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="J3:AG3"/>
+    <mergeCell ref="AH3:AS3"/>
+    <mergeCell ref="AT3:AX3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="R4:U4"/>
     <mergeCell ref="AO4:AQ4"/>
     <mergeCell ref="AR4:AS4"/>
     <mergeCell ref="V4:Y4"/>
@@ -6953,17 +6964,6 @@
     <mergeCell ref="AD4:AG4"/>
     <mergeCell ref="AH4:AJ4"/>
     <mergeCell ref="AK4:AN4"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="R4:U4"/>
-    <mergeCell ref="A1:AX1"/>
-    <mergeCell ref="A2:AX2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="J3:AG3"/>
-    <mergeCell ref="AH3:AS3"/>
-    <mergeCell ref="AT3:AX3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6984,810 +6984,810 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="24" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35">
+      <c r="A3" s="25">
         <v>1</v>
       </c>
-      <c r="B3" s="36" t="str">
+      <c r="B3" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT6</f>
         <v/>
       </c>
-      <c r="C3" s="36" t="str">
+      <c r="C3" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT6</f>
         <v/>
       </c>
-      <c r="D3" s="36" t="str">
+      <c r="D3" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU6</f>
         <v/>
       </c>
-      <c r="E3" s="36" t="str">
+      <c r="E3" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU6</f>
         <v/>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="26">
         <f>'ภาคเรียนที่ 1'!AV6</f>
         <v>0</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="26">
         <f>'ภาคเรียนที่ 2'!AV6</f>
         <v>0</v>
       </c>
-      <c r="H3" s="36">
+      <c r="H3" s="26">
         <f>'ภาคเรียนที่ 1'!AW6</f>
         <v>0</v>
       </c>
-      <c r="I3" s="36">
+      <c r="I3" s="26">
         <f>'ภาคเรียนที่ 2'!AW6</f>
         <v>0</v>
       </c>
-      <c r="J3" s="37"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35">
+      <c r="A4" s="25">
         <v>2</v>
       </c>
-      <c r="B4" s="36" t="str">
+      <c r="B4" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT7</f>
         <v/>
       </c>
-      <c r="C4" s="36" t="str">
+      <c r="C4" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT7</f>
         <v/>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU7</f>
         <v/>
       </c>
-      <c r="E4" s="36" t="str">
+      <c r="E4" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU7</f>
         <v/>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="26">
         <f>'ภาคเรียนที่ 1'!AV7</f>
         <v>0</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="26">
         <f>'ภาคเรียนที่ 2'!AV7</f>
         <v>0</v>
       </c>
-      <c r="H4" s="36">
+      <c r="H4" s="26">
         <f>'ภาคเรียนที่ 1'!AW7</f>
         <v>0</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="26">
         <f>'ภาคเรียนที่ 2'!AW7</f>
         <v>0</v>
       </c>
-      <c r="J4" s="37"/>
+      <c r="J4" s="27"/>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35">
+      <c r="A5" s="25">
         <v>3</v>
       </c>
-      <c r="B5" s="36" t="str">
+      <c r="B5" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT8</f>
         <v/>
       </c>
-      <c r="C5" s="36" t="str">
+      <c r="C5" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT8</f>
         <v/>
       </c>
-      <c r="D5" s="36" t="str">
+      <c r="D5" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU8</f>
         <v/>
       </c>
-      <c r="E5" s="36" t="str">
+      <c r="E5" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU8</f>
         <v/>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="26">
         <f>'ภาคเรียนที่ 1'!AV8</f>
         <v>0</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="26">
         <f>'ภาคเรียนที่ 2'!AV8</f>
         <v>0</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="26">
         <f>'ภาคเรียนที่ 1'!AW8</f>
         <v>0</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="26">
         <f>'ภาคเรียนที่ 2'!AW8</f>
         <v>0</v>
       </c>
-      <c r="J5" s="37"/>
+      <c r="J5" s="27"/>
     </row>
     <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="35">
+      <c r="A6" s="25">
         <v>4</v>
       </c>
-      <c r="B6" s="36" t="str">
+      <c r="B6" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT9</f>
         <v/>
       </c>
-      <c r="C6" s="36" t="str">
+      <c r="C6" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT9</f>
         <v/>
       </c>
-      <c r="D6" s="36" t="str">
+      <c r="D6" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU9</f>
         <v/>
       </c>
-      <c r="E6" s="36" t="str">
+      <c r="E6" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU9</f>
         <v/>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="26">
         <f>'ภาคเรียนที่ 1'!AV9</f>
         <v>0</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="26">
         <f>'ภาคเรียนที่ 2'!AV9</f>
         <v>0</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="26">
         <f>'ภาคเรียนที่ 1'!AW9</f>
         <v>0</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="26">
         <f>'ภาคเรียนที่ 2'!AW9</f>
         <v>0</v>
       </c>
-      <c r="J6" s="37"/>
+      <c r="J6" s="27"/>
     </row>
     <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35">
+      <c r="A7" s="25">
         <v>5</v>
       </c>
-      <c r="B7" s="36" t="str">
+      <c r="B7" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT10</f>
         <v/>
       </c>
-      <c r="C7" s="36" t="str">
+      <c r="C7" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT10</f>
         <v/>
       </c>
-      <c r="D7" s="36" t="str">
+      <c r="D7" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU10</f>
         <v/>
       </c>
-      <c r="E7" s="36" t="str">
+      <c r="E7" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU10</f>
         <v/>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="26">
         <f>'ภาคเรียนที่ 1'!AV10</f>
         <v>0</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="26">
         <f>'ภาคเรียนที่ 2'!AV10</f>
         <v>0</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="26">
         <f>'ภาคเรียนที่ 1'!AW10</f>
         <v>0</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="26">
         <f>'ภาคเรียนที่ 2'!AW10</f>
         <v>0</v>
       </c>
-      <c r="J7" s="37"/>
+      <c r="J7" s="27"/>
     </row>
     <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35">
+      <c r="A8" s="25">
         <v>6</v>
       </c>
-      <c r="B8" s="36" t="str">
+      <c r="B8" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT11</f>
         <v/>
       </c>
-      <c r="C8" s="36" t="str">
+      <c r="C8" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT11</f>
         <v/>
       </c>
-      <c r="D8" s="36" t="str">
+      <c r="D8" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU11</f>
         <v/>
       </c>
-      <c r="E8" s="36" t="str">
+      <c r="E8" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU11</f>
         <v/>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="26">
         <f>'ภาคเรียนที่ 1'!AV11</f>
         <v>0</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="26">
         <f>'ภาคเรียนที่ 2'!AV11</f>
         <v>0</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="26">
         <f>'ภาคเรียนที่ 1'!AW11</f>
         <v>0</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="26">
         <f>'ภาคเรียนที่ 2'!AW11</f>
         <v>0</v>
       </c>
-      <c r="J8" s="37"/>
+      <c r="J8" s="27"/>
     </row>
     <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35">
+      <c r="A9" s="25">
         <v>7</v>
       </c>
-      <c r="B9" s="36" t="str">
+      <c r="B9" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT12</f>
         <v/>
       </c>
-      <c r="C9" s="36" t="str">
+      <c r="C9" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT12</f>
         <v/>
       </c>
-      <c r="D9" s="36" t="str">
+      <c r="D9" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU12</f>
         <v/>
       </c>
-      <c r="E9" s="36" t="str">
+      <c r="E9" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU12</f>
         <v/>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="26">
         <f>'ภาคเรียนที่ 1'!AV12</f>
         <v>0</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="26">
         <f>'ภาคเรียนที่ 2'!AV12</f>
         <v>0</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="26">
         <f>'ภาคเรียนที่ 1'!AW12</f>
         <v>0</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="26">
         <f>'ภาคเรียนที่ 2'!AW12</f>
         <v>0</v>
       </c>
-      <c r="J9" s="37"/>
+      <c r="J9" s="27"/>
     </row>
     <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="35">
+      <c r="A10" s="25">
         <v>8</v>
       </c>
-      <c r="B10" s="36" t="str">
+      <c r="B10" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT13</f>
         <v/>
       </c>
-      <c r="C10" s="36" t="str">
+      <c r="C10" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT13</f>
         <v/>
       </c>
-      <c r="D10" s="36" t="str">
+      <c r="D10" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU13</f>
         <v/>
       </c>
-      <c r="E10" s="36" t="str">
+      <c r="E10" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU13</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="26">
         <f>'ภาคเรียนที่ 1'!AV13</f>
         <v>0</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="26">
         <f>'ภาคเรียนที่ 2'!AV13</f>
         <v>0</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="26">
         <f>'ภาคเรียนที่ 1'!AW13</f>
         <v>0</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="26">
         <f>'ภาคเรียนที่ 2'!AW13</f>
         <v>0</v>
       </c>
-      <c r="J10" s="37"/>
+      <c r="J10" s="27"/>
     </row>
     <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35">
+      <c r="A11" s="25">
         <v>9</v>
       </c>
-      <c r="B11" s="36" t="str">
+      <c r="B11" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT14</f>
         <v/>
       </c>
-      <c r="C11" s="36" t="str">
+      <c r="C11" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT14</f>
         <v/>
       </c>
-      <c r="D11" s="36" t="str">
+      <c r="D11" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU14</f>
         <v/>
       </c>
-      <c r="E11" s="36" t="str">
+      <c r="E11" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU14</f>
         <v/>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="26">
         <f>'ภาคเรียนที่ 1'!AV14</f>
         <v>0</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="26">
         <f>'ภาคเรียนที่ 2'!AV14</f>
         <v>0</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="26">
         <f>'ภาคเรียนที่ 1'!AW14</f>
         <v>0</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="26">
         <f>'ภาคเรียนที่ 2'!AW14</f>
         <v>0</v>
       </c>
-      <c r="J11" s="37"/>
+      <c r="J11" s="27"/>
     </row>
     <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="35">
+      <c r="A12" s="25">
         <v>10</v>
       </c>
-      <c r="B12" s="36" t="str">
+      <c r="B12" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT15</f>
         <v/>
       </c>
-      <c r="C12" s="36" t="str">
+      <c r="C12" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT15</f>
         <v/>
       </c>
-      <c r="D12" s="36" t="str">
+      <c r="D12" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU15</f>
         <v/>
       </c>
-      <c r="E12" s="36" t="str">
+      <c r="E12" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU15</f>
         <v/>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="26">
         <f>'ภาคเรียนที่ 1'!AV15</f>
         <v>0</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="26">
         <f>'ภาคเรียนที่ 2'!AV15</f>
         <v>0</v>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="26">
         <f>'ภาคเรียนที่ 1'!AW15</f>
         <v>0</v>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="26">
         <f>'ภาคเรียนที่ 2'!AW15</f>
         <v>0</v>
       </c>
-      <c r="J12" s="37"/>
+      <c r="J12" s="27"/>
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="35">
+      <c r="A13" s="25">
         <v>11</v>
       </c>
-      <c r="B13" s="36" t="str">
+      <c r="B13" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT16</f>
         <v/>
       </c>
-      <c r="C13" s="36" t="str">
+      <c r="C13" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT16</f>
         <v/>
       </c>
-      <c r="D13" s="36" t="str">
+      <c r="D13" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU16</f>
         <v/>
       </c>
-      <c r="E13" s="36" t="str">
+      <c r="E13" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU16</f>
         <v/>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="26">
         <f>'ภาคเรียนที่ 1'!AV16</f>
         <v>0</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="26">
         <f>'ภาคเรียนที่ 2'!AV16</f>
         <v>0</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="26">
         <f>'ภาคเรียนที่ 1'!AW16</f>
         <v>0</v>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="26">
         <f>'ภาคเรียนที่ 2'!AW16</f>
         <v>0</v>
       </c>
-      <c r="J13" s="37"/>
+      <c r="J13" s="27"/>
     </row>
     <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="35">
+      <c r="A14" s="25">
         <v>12</v>
       </c>
-      <c r="B14" s="36" t="str">
+      <c r="B14" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT17</f>
         <v/>
       </c>
-      <c r="C14" s="36" t="str">
+      <c r="C14" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT17</f>
         <v/>
       </c>
-      <c r="D14" s="36" t="str">
+      <c r="D14" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU17</f>
         <v/>
       </c>
-      <c r="E14" s="36" t="str">
+      <c r="E14" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU17</f>
         <v/>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="26">
         <f>'ภาคเรียนที่ 1'!AV17</f>
         <v>0</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="26">
         <f>'ภาคเรียนที่ 2'!AV17</f>
         <v>0</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="26">
         <f>'ภาคเรียนที่ 1'!AW17</f>
         <v>0</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="26">
         <f>'ภาคเรียนที่ 2'!AW17</f>
         <v>0</v>
       </c>
-      <c r="J14" s="37"/>
+      <c r="J14" s="27"/>
     </row>
     <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35">
+      <c r="A15" s="25">
         <v>13</v>
       </c>
-      <c r="B15" s="36" t="str">
+      <c r="B15" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT18</f>
         <v/>
       </c>
-      <c r="C15" s="36" t="str">
+      <c r="C15" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT18</f>
         <v/>
       </c>
-      <c r="D15" s="36" t="str">
+      <c r="D15" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU18</f>
         <v/>
       </c>
-      <c r="E15" s="36" t="str">
+      <c r="E15" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU18</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="26">
         <f>'ภาคเรียนที่ 1'!AV18</f>
         <v>0</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="26">
         <f>'ภาคเรียนที่ 2'!AV18</f>
         <v>0</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="26">
         <f>'ภาคเรียนที่ 1'!AW18</f>
         <v>0</v>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="26">
         <f>'ภาคเรียนที่ 2'!AW18</f>
         <v>0</v>
       </c>
-      <c r="J15" s="37"/>
+      <c r="J15" s="27"/>
     </row>
     <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="35">
+      <c r="A16" s="25">
         <v>14</v>
       </c>
-      <c r="B16" s="36" t="str">
+      <c r="B16" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT19</f>
         <v/>
       </c>
-      <c r="C16" s="36" t="str">
+      <c r="C16" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT19</f>
         <v/>
       </c>
-      <c r="D16" s="36" t="str">
+      <c r="D16" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU19</f>
         <v/>
       </c>
-      <c r="E16" s="36" t="str">
+      <c r="E16" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU19</f>
         <v/>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="26">
         <f>'ภาคเรียนที่ 1'!AV19</f>
         <v>0</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="26">
         <f>'ภาคเรียนที่ 2'!AV19</f>
         <v>0</v>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="26">
         <f>'ภาคเรียนที่ 1'!AW19</f>
         <v>0</v>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="26">
         <f>'ภาคเรียนที่ 2'!AW19</f>
         <v>0</v>
       </c>
-      <c r="J16" s="37"/>
+      <c r="J16" s="27"/>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35">
+      <c r="A17" s="25">
         <v>15</v>
       </c>
-      <c r="B17" s="36" t="str">
+      <c r="B17" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT20</f>
         <v/>
       </c>
-      <c r="C17" s="36" t="str">
+      <c r="C17" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT20</f>
         <v/>
       </c>
-      <c r="D17" s="36" t="str">
+      <c r="D17" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU20</f>
         <v/>
       </c>
-      <c r="E17" s="36" t="str">
+      <c r="E17" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU20</f>
         <v/>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="26">
         <f>'ภาคเรียนที่ 1'!AV20</f>
         <v>0</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="26">
         <f>'ภาคเรียนที่ 2'!AV20</f>
         <v>0</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="26">
         <f>'ภาคเรียนที่ 1'!AW20</f>
         <v>0</v>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="26">
         <f>'ภาคเรียนที่ 2'!AW20</f>
         <v>0</v>
       </c>
-      <c r="J17" s="37"/>
+      <c r="J17" s="27"/>
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="35">
+      <c r="A18" s="25">
         <v>16</v>
       </c>
-      <c r="B18" s="36" t="str">
+      <c r="B18" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT21</f>
         <v/>
       </c>
-      <c r="C18" s="36" t="str">
+      <c r="C18" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT21</f>
         <v/>
       </c>
-      <c r="D18" s="36" t="str">
+      <c r="D18" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU21</f>
         <v/>
       </c>
-      <c r="E18" s="36" t="str">
+      <c r="E18" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU21</f>
         <v/>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="26">
         <f>'ภาคเรียนที่ 1'!AV21</f>
         <v>0</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="26">
         <f>'ภาคเรียนที่ 2'!AV21</f>
         <v>0</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="26">
         <f>'ภาคเรียนที่ 1'!AW21</f>
         <v>0</v>
       </c>
-      <c r="I18" s="36">
+      <c r="I18" s="26">
         <f>'ภาคเรียนที่ 2'!AW21</f>
         <v>0</v>
       </c>
-      <c r="J18" s="37"/>
+      <c r="J18" s="27"/>
     </row>
     <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="35">
+      <c r="A19" s="25">
         <v>17</v>
       </c>
-      <c r="B19" s="36" t="str">
+      <c r="B19" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT22</f>
         <v/>
       </c>
-      <c r="C19" s="36" t="str">
+      <c r="C19" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT22</f>
         <v/>
       </c>
-      <c r="D19" s="36" t="str">
+      <c r="D19" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU22</f>
         <v/>
       </c>
-      <c r="E19" s="36" t="str">
+      <c r="E19" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU22</f>
         <v/>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="26">
         <f>'ภาคเรียนที่ 1'!AV22</f>
         <v>0</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="26">
         <f>'ภาคเรียนที่ 2'!AV22</f>
         <v>0</v>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="26">
         <f>'ภาคเรียนที่ 1'!AW22</f>
         <v>0</v>
       </c>
-      <c r="I19" s="36">
+      <c r="I19" s="26">
         <f>'ภาคเรียนที่ 2'!AW22</f>
         <v>0</v>
       </c>
-      <c r="J19" s="37"/>
+      <c r="J19" s="27"/>
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="35">
+      <c r="A20" s="25">
         <v>18</v>
       </c>
-      <c r="B20" s="36" t="str">
+      <c r="B20" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT23</f>
         <v/>
       </c>
-      <c r="C20" s="36" t="str">
+      <c r="C20" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT23</f>
         <v/>
       </c>
-      <c r="D20" s="36" t="str">
+      <c r="D20" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU23</f>
         <v/>
       </c>
-      <c r="E20" s="36" t="str">
+      <c r="E20" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU23</f>
         <v/>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="26">
         <f>'ภาคเรียนที่ 1'!AV23</f>
         <v>0</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="26">
         <f>'ภาคเรียนที่ 2'!AV23</f>
         <v>0</v>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="26">
         <f>'ภาคเรียนที่ 1'!AW23</f>
         <v>0</v>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="26">
         <f>'ภาคเรียนที่ 2'!AW23</f>
         <v>0</v>
       </c>
-      <c r="J20" s="37"/>
+      <c r="J20" s="27"/>
     </row>
     <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="35">
+      <c r="A21" s="25">
         <v>19</v>
       </c>
-      <c r="B21" s="36" t="str">
+      <c r="B21" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT24</f>
         <v/>
       </c>
-      <c r="C21" s="36" t="str">
+      <c r="C21" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT24</f>
         <v/>
       </c>
-      <c r="D21" s="36" t="str">
+      <c r="D21" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU24</f>
         <v/>
       </c>
-      <c r="E21" s="36" t="str">
+      <c r="E21" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU24</f>
         <v/>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="26">
         <f>'ภาคเรียนที่ 1'!AV24</f>
         <v>0</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="26">
         <f>'ภาคเรียนที่ 2'!AV24</f>
         <v>0</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="26">
         <f>'ภาคเรียนที่ 1'!AW24</f>
         <v>0</v>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="26">
         <f>'ภาคเรียนที่ 2'!AW24</f>
         <v>0</v>
       </c>
-      <c r="J21" s="37"/>
+      <c r="J21" s="27"/>
     </row>
     <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="35">
+      <c r="A22" s="25">
         <v>20</v>
       </c>
-      <c r="B22" s="36" t="str">
+      <c r="B22" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AT25</f>
         <v/>
       </c>
-      <c r="C22" s="36" t="str">
+      <c r="C22" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AT25</f>
         <v/>
       </c>
-      <c r="D22" s="36" t="str">
+      <c r="D22" s="26" t="str">
         <f>'ภาคเรียนที่ 1'!AU25</f>
         <v/>
       </c>
-      <c r="E22" s="36" t="str">
+      <c r="E22" s="26" t="str">
         <f>'ภาคเรียนที่ 2'!AU25</f>
         <v/>
       </c>
-      <c r="F22" s="36">
+      <c r="F22" s="26">
         <f>'ภาคเรียนที่ 1'!AV25</f>
         <v>0</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="26">
         <f>'ภาคเรียนที่ 2'!AV25</f>
         <v>0</v>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="26">
         <f>'ภาคเรียนที่ 1'!AW25</f>
         <v>0</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="26">
         <f>'ภาคเรียนที่ 2'!AW25</f>
         <v>0</v>
       </c>
-      <c r="J22" s="37"/>
+      <c r="J22" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7809,118 +7809,118 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
     </row>
     <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="29" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="41"/>
+      <c r="D3" s="31"/>
     </row>
     <row r="4" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="42"/>
-      <c r="C4" s="43" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="43"/>
+      <c r="D4" s="33"/>
     </row>
     <row r="5" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="40"/>
-      <c r="C5" s="41" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="41"/>
+      <c r="D5" s="31"/>
     </row>
     <row r="6" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="33" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="41"/>
+      <c r="D7" s="31"/>
     </row>
     <row r="8" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="43"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="41"/>
+      <c r="D9" s="31"/>
     </row>
     <row r="10" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="33" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="41"/>
+      <c r="D11" s="31"/>
     </row>
     <row r="12" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="42"/>
-      <c r="C12" s="43" t="s">
+      <c r="B12" s="32"/>
+      <c r="C12" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="43"/>
+      <c r="D12" s="33"/>
     </row>
     <row r="13" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="40"/>
-      <c r="C13" s="41" t="s">
+      <c r="B13" s="30"/>
+      <c r="C13" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="41"/>
+      <c r="D13" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
